--- a/datasets/QHI_roots_data/ald_elevation_slope_coordinates .xlsx
+++ b/datasets/QHI_roots_data/ald_elevation_slope_coordinates .xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uoe-my.sharepoint.com/personal/s2277781_ed_ac_uk/Documents/Dissertation/Data/QHI_root_data/alds/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7618DD66-756C-4988-B8CD-D929309F2627}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="81" documentId="8_{7618DD66-756C-4988-B8CD-D929309F2627}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5CCCEC99-6361-4572-B15F-554A5E050006}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{5A4F7802-2836-4E57-BA63-1607F58E9FFC}"/>
+    <workbookView xWindow="-83" yWindow="0" windowWidth="10965" windowHeight="12863" xr2:uid="{5A4F7802-2836-4E57-BA63-1607F58E9FFC}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="457" uniqueCount="16">
   <si>
     <t>ald</t>
   </si>
@@ -81,6 +81,9 @@
   </si>
   <si>
     <t>thaw_av</t>
+  </si>
+  <si>
+    <t>year</t>
   </si>
 </sst>
 </file>
@@ -476,13 +479,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{50281568-64F3-449A-B2BE-5A1CF6C7EB2A}">
-  <dimension ref="A1:H65"/>
+  <dimension ref="A1:I225"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="2" max="2" width="24.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:9">
       <c r="A1" t="s">
         <v>7</v>
       </c>
@@ -496,19 +499,22 @@
         <v>10</v>
       </c>
       <c r="E1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F1" t="s">
         <v>11</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>12</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>13</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:8">
+    <row r="2" spans="1:9">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -521,20 +527,23 @@
       <c r="D2">
         <v>-138.86307059999999</v>
       </c>
-      <c r="E2" s="2">
+      <c r="E2">
+        <v>2023</v>
+      </c>
+      <c r="F2" s="2">
         <v>71.664990000000003</v>
       </c>
-      <c r="F2" s="2">
+      <c r="G2" s="2">
         <v>1.0686739999999999</v>
       </c>
-      <c r="G2" s="3">
+      <c r="H2" s="3">
         <v>216</v>
       </c>
-      <c r="H2">
+      <c r="I2">
         <v>49.866666666666667</v>
       </c>
     </row>
-    <row r="3" spans="1:8">
+    <row r="3" spans="1:9">
       <c r="A3" t="s">
         <v>0</v>
       </c>
@@ -547,20 +556,23 @@
       <c r="D3">
         <v>-138.8631728</v>
       </c>
-      <c r="E3" s="2">
+      <c r="E3">
+        <v>2023</v>
+      </c>
+      <c r="F3" s="2">
         <v>71.566590000000005</v>
       </c>
-      <c r="F3" s="2">
+      <c r="G3" s="2">
         <v>3.236253</v>
       </c>
-      <c r="G3" s="3">
+      <c r="H3" s="3">
         <v>216</v>
       </c>
-      <c r="H3">
+      <c r="I3">
         <v>47.366666666666667</v>
       </c>
     </row>
-    <row r="4" spans="1:8">
+    <row r="4" spans="1:9">
       <c r="A4" t="s">
         <v>0</v>
       </c>
@@ -573,20 +585,23 @@
       <c r="D4">
         <v>-138.8634658</v>
       </c>
-      <c r="E4" s="2">
+      <c r="E4">
+        <v>2023</v>
+      </c>
+      <c r="F4" s="2">
         <v>71.334130000000002</v>
       </c>
-      <c r="F4" s="2">
+      <c r="G4" s="2">
         <v>2.6920440000000001</v>
       </c>
-      <c r="G4" s="3">
+      <c r="H4" s="3">
         <v>216</v>
       </c>
-      <c r="H4">
+      <c r="I4">
         <v>45.79999999999999</v>
       </c>
     </row>
-    <row r="5" spans="1:8">
+    <row r="5" spans="1:9">
       <c r="A5" t="s">
         <v>0</v>
       </c>
@@ -599,20 +614,23 @@
       <c r="D5">
         <v>-138.8637913</v>
       </c>
-      <c r="E5" s="2">
+      <c r="E5">
+        <v>2023</v>
+      </c>
+      <c r="F5" s="2">
         <v>71.194389999999999</v>
       </c>
-      <c r="F5" s="2">
+      <c r="G5" s="2">
         <v>1.1705080000000001</v>
       </c>
-      <c r="G5" s="3">
+      <c r="H5" s="3">
         <v>216</v>
       </c>
-      <c r="H5">
+      <c r="I5">
         <v>42.5</v>
       </c>
     </row>
-    <row r="6" spans="1:8">
+    <row r="6" spans="1:9">
       <c r="A6" t="s">
         <v>0</v>
       </c>
@@ -625,20 +643,23 @@
       <c r="D6">
         <v>-138.86387010000001</v>
       </c>
-      <c r="E6" s="2">
+      <c r="E6">
+        <v>2023</v>
+      </c>
+      <c r="F6" s="2">
         <v>71.170460000000006</v>
       </c>
-      <c r="F6" s="2">
+      <c r="G6" s="2">
         <v>1.1862360000000001</v>
       </c>
-      <c r="G6" s="3">
+      <c r="H6" s="3">
         <v>216</v>
       </c>
-      <c r="H6">
+      <c r="I6">
         <v>43.166666666666664</v>
       </c>
     </row>
-    <row r="7" spans="1:8">
+    <row r="7" spans="1:9">
       <c r="A7" t="s">
         <v>0</v>
       </c>
@@ -651,20 +672,23 @@
       <c r="D7">
         <v>-138.8640747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="E7">
+        <v>2023</v>
+      </c>
+      <c r="F7" s="2">
         <v>71.030659999999997</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>1.785264</v>
       </c>
-      <c r="G7" s="3">
+      <c r="H7" s="3">
         <v>216</v>
       </c>
-      <c r="H7">
+      <c r="I7">
         <v>54.233333333333327</v>
       </c>
     </row>
-    <row r="8" spans="1:8">
+    <row r="8" spans="1:9">
       <c r="A8" t="s">
         <v>0</v>
       </c>
@@ -677,20 +701,23 @@
       <c r="D8">
         <v>-138.86817970000001</v>
       </c>
-      <c r="E8" s="2">
+      <c r="E8">
+        <v>2023</v>
+      </c>
+      <c r="F8" s="2">
         <v>71.11157</v>
       </c>
-      <c r="F8" s="2">
+      <c r="G8" s="2">
         <v>3.3767399999999999</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>216</v>
       </c>
-      <c r="H8">
+      <c r="I8">
         <v>66.099999999999994</v>
       </c>
     </row>
-    <row r="9" spans="1:8">
+    <row r="9" spans="1:9">
       <c r="A9" t="s">
         <v>0</v>
       </c>
@@ -703,20 +730,23 @@
       <c r="D9">
         <v>-138.86811879999999</v>
       </c>
-      <c r="E9" s="2">
+      <c r="E9">
+        <v>2023</v>
+      </c>
+      <c r="F9" s="2">
         <v>71.146529999999998</v>
       </c>
-      <c r="F9" s="2">
+      <c r="G9" s="2">
         <v>2.5742989999999999</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>216</v>
       </c>
-      <c r="H9">
+      <c r="I9">
         <v>72.133333333333326</v>
       </c>
     </row>
-    <row r="10" spans="1:8">
+    <row r="10" spans="1:9">
       <c r="A10" t="s">
         <v>0</v>
       </c>
@@ -729,20 +759,23 @@
       <c r="D10">
         <v>-138.86773909999999</v>
       </c>
-      <c r="E10" s="2">
+      <c r="E10">
+        <v>2023</v>
+      </c>
+      <c r="F10" s="2">
         <v>71.806269999999998</v>
       </c>
-      <c r="F10" s="2">
+      <c r="G10" s="2">
         <v>4.376296</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>216</v>
       </c>
-      <c r="H10">
+      <c r="I10">
         <v>69.633333333333326</v>
       </c>
     </row>
-    <row r="11" spans="1:8">
+    <row r="11" spans="1:9">
       <c r="A11" t="s">
         <v>0</v>
       </c>
@@ -755,20 +788,23 @@
       <c r="D11">
         <v>-138.8676384</v>
       </c>
-      <c r="E11" s="2">
+      <c r="E11">
+        <v>2023</v>
+      </c>
+      <c r="F11" s="2">
         <v>71.979259999999996</v>
       </c>
-      <c r="F11" s="2">
+      <c r="G11" s="2">
         <v>4.6941449999999998</v>
       </c>
-      <c r="G11" s="3">
+      <c r="H11" s="3">
         <v>216</v>
       </c>
-      <c r="H11">
+      <c r="I11">
         <v>77.7</v>
       </c>
     </row>
-    <row r="12" spans="1:8">
+    <row r="12" spans="1:9">
       <c r="A12" t="s">
         <v>0</v>
       </c>
@@ -781,20 +817,23 @@
       <c r="D12">
         <v>-138.86729539999999</v>
       </c>
-      <c r="E12" s="2">
+      <c r="E12">
+        <v>2023</v>
+      </c>
+      <c r="F12" s="2">
         <v>72.876679999999993</v>
       </c>
-      <c r="F12" s="2">
+      <c r="G12" s="2">
         <v>2.3661750000000001</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>216</v>
       </c>
-      <c r="H12">
+      <c r="I12">
         <v>72.466666666666654</v>
       </c>
     </row>
-    <row r="13" spans="1:8">
+    <row r="13" spans="1:9">
       <c r="A13" t="s">
         <v>0</v>
       </c>
@@ -807,20 +846,23 @@
       <c r="D13">
         <v>-138.86699780000001</v>
       </c>
-      <c r="E13" s="2">
+      <c r="E13">
+        <v>2023</v>
+      </c>
+      <c r="F13" s="2">
         <v>73.514600000000002</v>
       </c>
-      <c r="F13" s="2">
+      <c r="G13" s="2">
         <v>4.204345</v>
       </c>
-      <c r="G13" s="3">
+      <c r="H13" s="3">
         <v>216</v>
       </c>
-      <c r="H13">
+      <c r="I13">
         <v>69.166666666666671</v>
       </c>
     </row>
-    <row r="14" spans="1:8">
+    <row r="14" spans="1:9">
       <c r="A14" t="s">
         <v>0</v>
       </c>
@@ -833,20 +875,23 @@
       <c r="D14">
         <v>-138.91274999999999</v>
       </c>
-      <c r="E14" s="2">
+      <c r="E14">
+        <v>2023</v>
+      </c>
+      <c r="F14" s="2">
         <v>57.668939999999999</v>
       </c>
-      <c r="F14" s="2">
+      <c r="G14" s="2">
         <v>2.7936839999999998</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>216</v>
       </c>
-      <c r="H14">
+      <c r="I14">
         <v>41.533333333333331</v>
       </c>
     </row>
-    <row r="15" spans="1:8">
+    <row r="15" spans="1:9">
       <c r="A15" t="s">
         <v>0</v>
       </c>
@@ -859,20 +904,23 @@
       <c r="D15">
         <v>-138.91274999999999</v>
       </c>
-      <c r="E15" s="2">
+      <c r="E15">
+        <v>2023</v>
+      </c>
+      <c r="F15" s="2">
         <v>57.668939999999999</v>
       </c>
-      <c r="F15" s="2">
+      <c r="G15" s="2">
         <v>2.7936839999999998</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>216</v>
       </c>
-      <c r="H15">
+      <c r="I15">
         <v>49.066666666666663</v>
       </c>
     </row>
-    <row r="16" spans="1:8">
+    <row r="16" spans="1:9">
       <c r="A16" t="s">
         <v>0</v>
       </c>
@@ -885,20 +933,23 @@
       <c r="D16">
         <v>-138.91274999999999</v>
       </c>
-      <c r="E16" s="2">
+      <c r="E16">
+        <v>2023</v>
+      </c>
+      <c r="F16" s="2">
         <v>57.668939999999999</v>
       </c>
-      <c r="F16" s="2">
+      <c r="G16" s="2">
         <v>2.7936839999999998</v>
       </c>
-      <c r="G16" s="3">
+      <c r="H16" s="3">
         <v>216</v>
       </c>
-      <c r="H16">
+      <c r="I16">
         <v>52.366666666666674</v>
       </c>
     </row>
-    <row r="17" spans="1:8">
+    <row r="17" spans="1:9">
       <c r="A17" t="s">
         <v>0</v>
       </c>
@@ -911,20 +962,23 @@
       <c r="D17">
         <v>-138.91274999999999</v>
       </c>
-      <c r="E17" s="2">
+      <c r="E17">
+        <v>2023</v>
+      </c>
+      <c r="F17" s="2">
         <v>57.668939999999999</v>
       </c>
-      <c r="F17" s="2">
+      <c r="G17" s="2">
         <v>2.7936839999999998</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>216</v>
       </c>
-      <c r="H17">
+      <c r="I17">
         <v>47.866666666666674</v>
       </c>
     </row>
-    <row r="18" spans="1:8">
+    <row r="18" spans="1:9">
       <c r="A18" t="s">
         <v>0</v>
       </c>
@@ -937,20 +991,23 @@
       <c r="D18">
         <v>-138.90445</v>
       </c>
-      <c r="E18" s="2">
+      <c r="E18">
+        <v>2023</v>
+      </c>
+      <c r="F18" s="2">
         <v>28.906300000000002</v>
       </c>
-      <c r="F18" s="2">
+      <c r="G18" s="2">
         <v>4.0111990000000004</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>216</v>
       </c>
-      <c r="H18">
+      <c r="I18">
         <v>79.63333333333334</v>
       </c>
     </row>
-    <row r="19" spans="1:8">
+    <row r="19" spans="1:9">
       <c r="A19" t="s">
         <v>0</v>
       </c>
@@ -963,20 +1020,23 @@
       <c r="D19">
         <v>-138.90445</v>
       </c>
-      <c r="E19" s="2">
+      <c r="E19">
+        <v>2023</v>
+      </c>
+      <c r="F19" s="2">
         <v>28.906300000000002</v>
       </c>
-      <c r="F19" s="2">
+      <c r="G19" s="2">
         <v>4.0111990000000004</v>
       </c>
-      <c r="G19" s="3">
+      <c r="H19" s="3">
         <v>216</v>
       </c>
-      <c r="H19">
+      <c r="I19">
         <v>86.833333333333329</v>
       </c>
     </row>
-    <row r="20" spans="1:8">
+    <row r="20" spans="1:9">
       <c r="A20" t="s">
         <v>0</v>
       </c>
@@ -989,20 +1049,23 @@
       <c r="D20">
         <v>-138.90445</v>
       </c>
-      <c r="E20" s="2">
+      <c r="E20">
+        <v>2023</v>
+      </c>
+      <c r="F20" s="2">
         <v>28.906300000000002</v>
       </c>
-      <c r="F20" s="2">
+      <c r="G20" s="2">
         <v>4.0111990000000004</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>216</v>
       </c>
-      <c r="H20">
+      <c r="I20">
         <v>81.466666666666654</v>
       </c>
     </row>
-    <row r="21" spans="1:8">
+    <row r="21" spans="1:9">
       <c r="A21" t="s">
         <v>0</v>
       </c>
@@ -1015,20 +1078,23 @@
       <c r="D21">
         <v>-138.90445</v>
       </c>
-      <c r="E21" s="2">
+      <c r="E21">
+        <v>2023</v>
+      </c>
+      <c r="F21" s="2">
         <v>28.906300000000002</v>
       </c>
-      <c r="F21" s="2">
+      <c r="G21" s="2">
         <v>4.0111990000000004</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>216</v>
       </c>
-      <c r="H21">
+      <c r="I21">
         <v>79.666666666666671</v>
       </c>
     </row>
-    <row r="22" spans="1:8">
+    <row r="22" spans="1:9">
       <c r="A22" t="s">
         <v>0</v>
       </c>
@@ -1041,20 +1107,23 @@
       <c r="D22">
         <v>-138.86307059999999</v>
       </c>
-      <c r="E22" s="2">
+      <c r="E22">
+        <v>2023</v>
+      </c>
+      <c r="F22" s="2">
         <v>71.664990000000003</v>
       </c>
-      <c r="F22" s="2">
+      <c r="G22" s="2">
         <v>1.0686739999999999</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>181</v>
       </c>
-      <c r="H22">
+      <c r="I22">
         <v>29.966666666666669</v>
       </c>
     </row>
-    <row r="23" spans="1:8">
+    <row r="23" spans="1:9">
       <c r="A23" t="s">
         <v>0</v>
       </c>
@@ -1067,20 +1136,23 @@
       <c r="D23">
         <v>-138.8631728</v>
       </c>
-      <c r="E23" s="2">
+      <c r="E23">
+        <v>2023</v>
+      </c>
+      <c r="F23" s="2">
         <v>71.566590000000005</v>
       </c>
-      <c r="F23" s="2">
+      <c r="G23" s="2">
         <v>3.236253</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>181</v>
       </c>
-      <c r="H23">
+      <c r="I23">
         <v>28.333333333333332</v>
       </c>
     </row>
-    <row r="24" spans="1:8">
+    <row r="24" spans="1:9">
       <c r="A24" t="s">
         <v>0</v>
       </c>
@@ -1093,20 +1165,23 @@
       <c r="D24">
         <v>-138.8634658</v>
       </c>
-      <c r="E24" s="2">
+      <c r="E24">
+        <v>2023</v>
+      </c>
+      <c r="F24" s="2">
         <v>71.334130000000002</v>
       </c>
-      <c r="F24" s="2">
+      <c r="G24" s="2">
         <v>2.6920440000000001</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>181</v>
       </c>
-      <c r="H24">
+      <c r="I24">
         <v>23.266666666666669</v>
       </c>
     </row>
-    <row r="25" spans="1:8">
+    <row r="25" spans="1:9">
       <c r="A25" t="s">
         <v>0</v>
       </c>
@@ -1119,20 +1194,23 @@
       <c r="D25">
         <v>-138.8637913</v>
       </c>
-      <c r="E25" s="2">
+      <c r="E25">
+        <v>2023</v>
+      </c>
+      <c r="F25" s="2">
         <v>71.194389999999999</v>
       </c>
-      <c r="F25" s="2">
+      <c r="G25" s="2">
         <v>1.1705080000000001</v>
       </c>
-      <c r="G25" s="3">
+      <c r="H25" s="3">
         <v>181</v>
       </c>
-      <c r="H25">
+      <c r="I25">
         <v>21.666666666666668</v>
       </c>
     </row>
-    <row r="26" spans="1:8">
+    <row r="26" spans="1:9">
       <c r="A26" t="s">
         <v>0</v>
       </c>
@@ -1145,20 +1223,23 @@
       <c r="D26">
         <v>-138.86387010000001</v>
       </c>
-      <c r="E26" s="2">
+      <c r="E26">
+        <v>2023</v>
+      </c>
+      <c r="F26" s="2">
         <v>71.170460000000006</v>
       </c>
-      <c r="F26" s="2">
+      <c r="G26" s="2">
         <v>1.1862360000000001</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>181</v>
       </c>
-      <c r="H26">
+      <c r="I26">
         <v>18.633333333333336</v>
       </c>
     </row>
-    <row r="27" spans="1:8">
+    <row r="27" spans="1:9">
       <c r="A27" t="s">
         <v>0</v>
       </c>
@@ -1171,20 +1252,23 @@
       <c r="D27">
         <v>-138.8640747</v>
       </c>
-      <c r="E27" s="2">
+      <c r="E27">
+        <v>2023</v>
+      </c>
+      <c r="F27" s="2">
         <v>71.030659999999997</v>
       </c>
-      <c r="F27" s="2">
+      <c r="G27" s="2">
         <v>1.785264</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>181</v>
       </c>
-      <c r="H27">
+      <c r="I27">
         <v>35.733333333333334</v>
       </c>
     </row>
-    <row r="28" spans="1:8">
+    <row r="28" spans="1:9">
       <c r="A28" t="s">
         <v>0</v>
       </c>
@@ -1197,20 +1281,23 @@
       <c r="D28">
         <v>-138.86817970000001</v>
       </c>
-      <c r="E28" s="2">
+      <c r="E28">
+        <v>2023</v>
+      </c>
+      <c r="F28" s="2">
         <v>71.11157</v>
       </c>
-      <c r="F28" s="2">
+      <c r="G28" s="2">
         <v>3.3767399999999999</v>
       </c>
-      <c r="G28" s="3">
+      <c r="H28" s="3">
         <v>181</v>
       </c>
-      <c r="H28">
+      <c r="I28">
         <v>31.099999999999998</v>
       </c>
     </row>
-    <row r="29" spans="1:8">
+    <row r="29" spans="1:9">
       <c r="A29" t="s">
         <v>0</v>
       </c>
@@ -1223,20 +1310,23 @@
       <c r="D29">
         <v>-138.86811879999999</v>
       </c>
-      <c r="E29" s="2">
+      <c r="E29">
+        <v>2023</v>
+      </c>
+      <c r="F29" s="2">
         <v>71.146529999999998</v>
       </c>
-      <c r="F29" s="2">
+      <c r="G29" s="2">
         <v>2.5742989999999999</v>
       </c>
-      <c r="G29" s="3">
+      <c r="H29" s="3">
         <v>181</v>
       </c>
-      <c r="H29">
+      <c r="I29">
         <v>39.533333333333331</v>
       </c>
     </row>
-    <row r="30" spans="1:8">
+    <row r="30" spans="1:9">
       <c r="A30" t="s">
         <v>0</v>
       </c>
@@ -1249,20 +1339,23 @@
       <c r="D30">
         <v>-138.86773909999999</v>
       </c>
-      <c r="E30" s="2">
+      <c r="E30">
+        <v>2023</v>
+      </c>
+      <c r="F30" s="2">
         <v>71.806269999999998</v>
       </c>
-      <c r="F30" s="2">
+      <c r="G30" s="2">
         <v>4.376296</v>
       </c>
-      <c r="G30" s="3">
+      <c r="H30" s="3">
         <v>181</v>
       </c>
-      <c r="H30">
+      <c r="I30">
         <v>35.9</v>
       </c>
     </row>
-    <row r="31" spans="1:8">
+    <row r="31" spans="1:9">
       <c r="A31" t="s">
         <v>0</v>
       </c>
@@ -1275,20 +1368,23 @@
       <c r="D31">
         <v>-138.8676384</v>
       </c>
-      <c r="E31" s="2">
+      <c r="E31">
+        <v>2023</v>
+      </c>
+      <c r="F31" s="2">
         <v>71.979259999999996</v>
       </c>
-      <c r="F31" s="2">
+      <c r="G31" s="2">
         <v>4.6941449999999998</v>
       </c>
-      <c r="G31" s="3">
+      <c r="H31" s="3">
         <v>181</v>
       </c>
-      <c r="H31">
+      <c r="I31">
         <v>33.433333333333337</v>
       </c>
     </row>
-    <row r="32" spans="1:8">
+    <row r="32" spans="1:9">
       <c r="A32" t="s">
         <v>0</v>
       </c>
@@ -1301,20 +1397,23 @@
       <c r="D32">
         <v>-138.86729539999999</v>
       </c>
-      <c r="E32" s="2">
+      <c r="E32">
+        <v>2023</v>
+      </c>
+      <c r="F32" s="2">
         <v>72.876679999999993</v>
       </c>
-      <c r="F32" s="2">
+      <c r="G32" s="2">
         <v>2.3661750000000001</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>181</v>
       </c>
-      <c r="H32">
+      <c r="I32">
         <v>39.566666666666663</v>
       </c>
     </row>
-    <row r="33" spans="1:8">
+    <row r="33" spans="1:9">
       <c r="A33" t="s">
         <v>0</v>
       </c>
@@ -1327,20 +1426,23 @@
       <c r="D33">
         <v>-138.86699780000001</v>
       </c>
-      <c r="E33" s="2">
+      <c r="E33">
+        <v>2023</v>
+      </c>
+      <c r="F33" s="2">
         <v>73.514600000000002</v>
       </c>
-      <c r="F33" s="2">
+      <c r="G33" s="2">
         <v>4.204345</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>181</v>
       </c>
-      <c r="H33">
+      <c r="I33">
         <v>38.066666666666663</v>
       </c>
     </row>
-    <row r="34" spans="1:8">
+    <row r="34" spans="1:9">
       <c r="A34" t="s">
         <v>0</v>
       </c>
@@ -1353,20 +1455,23 @@
       <c r="D34">
         <v>-138.91274999999999</v>
       </c>
-      <c r="E34" s="2">
+      <c r="E34">
+        <v>2023</v>
+      </c>
+      <c r="F34" s="2">
         <v>57.668939999999999</v>
       </c>
-      <c r="F34" s="2">
+      <c r="G34" s="2">
         <v>2.7936839999999998</v>
       </c>
-      <c r="G34" s="3">
+      <c r="H34" s="3">
         <v>181</v>
       </c>
-      <c r="H34">
+      <c r="I34">
         <v>22.466666666666669</v>
       </c>
     </row>
-    <row r="35" spans="1:8">
+    <row r="35" spans="1:9">
       <c r="A35" t="s">
         <v>0</v>
       </c>
@@ -1379,20 +1484,23 @@
       <c r="D35">
         <v>-138.91274999999999</v>
       </c>
-      <c r="E35" s="2">
+      <c r="E35">
+        <v>2023</v>
+      </c>
+      <c r="F35" s="2">
         <v>57.668939999999999</v>
       </c>
-      <c r="F35" s="2">
+      <c r="G35" s="2">
         <v>2.7936839999999998</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>181</v>
       </c>
-      <c r="H35">
+      <c r="I35">
         <v>32.06666666666667</v>
       </c>
     </row>
-    <row r="36" spans="1:8">
+    <row r="36" spans="1:9">
       <c r="A36" t="s">
         <v>0</v>
       </c>
@@ -1405,20 +1513,23 @@
       <c r="D36">
         <v>-138.91274999999999</v>
       </c>
-      <c r="E36" s="2">
+      <c r="E36">
+        <v>2023</v>
+      </c>
+      <c r="F36" s="2">
         <v>57.668939999999999</v>
       </c>
-      <c r="F36" s="2">
+      <c r="G36" s="2">
         <v>2.7936839999999998</v>
       </c>
-      <c r="G36" s="3">
+      <c r="H36" s="3">
         <v>181</v>
       </c>
-      <c r="H36">
+      <c r="I36">
         <v>31.933333333333337</v>
       </c>
     </row>
-    <row r="37" spans="1:8">
+    <row r="37" spans="1:9">
       <c r="A37" t="s">
         <v>0</v>
       </c>
@@ -1431,20 +1542,23 @@
       <c r="D37">
         <v>-138.91274999999999</v>
       </c>
-      <c r="E37" s="2">
+      <c r="E37">
+        <v>2023</v>
+      </c>
+      <c r="F37" s="2">
         <v>57.668939999999999</v>
       </c>
-      <c r="F37" s="2">
+      <c r="G37" s="2">
         <v>2.7936839999999998</v>
       </c>
-      <c r="G37" s="3">
+      <c r="H37" s="3">
         <v>181</v>
       </c>
-      <c r="H37">
+      <c r="I37">
         <v>25.266666666666666</v>
       </c>
     </row>
-    <row r="38" spans="1:8">
+    <row r="38" spans="1:9">
       <c r="A38" t="s">
         <v>0</v>
       </c>
@@ -1457,20 +1571,23 @@
       <c r="D38">
         <v>-138.90445</v>
       </c>
-      <c r="E38" s="2">
+      <c r="E38">
+        <v>2023</v>
+      </c>
+      <c r="F38" s="2">
         <v>28.906300000000002</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>4.0111990000000004</v>
       </c>
-      <c r="G38" s="3">
+      <c r="H38" s="3">
         <v>181</v>
       </c>
-      <c r="H38">
+      <c r="I38">
         <v>52.300000000000004</v>
       </c>
     </row>
-    <row r="39" spans="1:8">
+    <row r="39" spans="1:9">
       <c r="A39" t="s">
         <v>0</v>
       </c>
@@ -1483,20 +1600,23 @@
       <c r="D39">
         <v>-138.90445</v>
       </c>
-      <c r="E39" s="2">
+      <c r="E39">
+        <v>2023</v>
+      </c>
+      <c r="F39" s="2">
         <v>28.906300000000002</v>
       </c>
-      <c r="F39" s="2">
+      <c r="G39" s="2">
         <v>4.0111990000000004</v>
       </c>
-      <c r="G39" s="3">
+      <c r="H39" s="3">
         <v>181</v>
       </c>
-      <c r="H39">
+      <c r="I39">
         <v>48.366666666666667</v>
       </c>
     </row>
-    <row r="40" spans="1:8">
+    <row r="40" spans="1:9">
       <c r="A40" t="s">
         <v>0</v>
       </c>
@@ -1509,20 +1629,23 @@
       <c r="D40">
         <v>-138.90445</v>
       </c>
-      <c r="E40" s="2">
+      <c r="E40">
+        <v>2023</v>
+      </c>
+      <c r="F40" s="2">
         <v>28.906300000000002</v>
       </c>
-      <c r="F40" s="2">
+      <c r="G40" s="2">
         <v>4.0111990000000004</v>
       </c>
-      <c r="G40" s="3">
+      <c r="H40" s="3">
         <v>181</v>
       </c>
-      <c r="H40">
+      <c r="I40">
         <v>41.733333333333327</v>
       </c>
     </row>
-    <row r="41" spans="1:8">
+    <row r="41" spans="1:9">
       <c r="A41" t="s">
         <v>0</v>
       </c>
@@ -1535,20 +1658,23 @@
       <c r="D41">
         <v>-138.90445</v>
       </c>
-      <c r="E41" s="2">
+      <c r="E41">
+        <v>2023</v>
+      </c>
+      <c r="F41" s="2">
         <v>28.906300000000002</v>
       </c>
-      <c r="F41" s="2">
+      <c r="G41" s="2">
         <v>4.0111990000000004</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>181</v>
       </c>
-      <c r="H41">
+      <c r="I41">
         <v>42.666666666666664</v>
       </c>
     </row>
-    <row r="42" spans="1:8">
+    <row r="42" spans="1:9">
       <c r="A42" t="s">
         <v>0</v>
       </c>
@@ -1561,20 +1687,23 @@
       <c r="D42">
         <v>-138.86307059999999</v>
       </c>
-      <c r="E42" s="2">
+      <c r="E42">
+        <v>2023</v>
+      </c>
+      <c r="F42" s="2">
         <v>71.664990000000003</v>
       </c>
-      <c r="F42" s="2">
+      <c r="G42" s="2">
         <v>1.0686739999999999</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>228</v>
       </c>
-      <c r="H42">
+      <c r="I42">
         <v>50.233333333333327</v>
       </c>
     </row>
-    <row r="43" spans="1:8">
+    <row r="43" spans="1:9">
       <c r="A43" t="s">
         <v>0</v>
       </c>
@@ -1587,20 +1716,23 @@
       <c r="D43">
         <v>-138.8631728</v>
       </c>
-      <c r="E43" s="2">
+      <c r="E43">
+        <v>2023</v>
+      </c>
+      <c r="F43" s="2">
         <v>71.566590000000005</v>
       </c>
-      <c r="F43" s="2">
+      <c r="G43" s="2">
         <v>3.236253</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>228</v>
       </c>
-      <c r="H43">
+      <c r="I43">
         <v>52</v>
       </c>
     </row>
-    <row r="44" spans="1:8">
+    <row r="44" spans="1:9">
       <c r="A44" t="s">
         <v>0</v>
       </c>
@@ -1613,20 +1745,23 @@
       <c r="D44">
         <v>-138.8634658</v>
       </c>
-      <c r="E44" s="2">
+      <c r="E44">
+        <v>2023</v>
+      </c>
+      <c r="F44" s="2">
         <v>71.334130000000002</v>
       </c>
-      <c r="F44" s="2">
+      <c r="G44" s="2">
         <v>2.6920440000000001</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>228</v>
       </c>
-      <c r="H44">
+      <c r="I44">
         <v>44.466666666666661</v>
       </c>
     </row>
-    <row r="45" spans="1:8">
+    <row r="45" spans="1:9">
       <c r="A45" t="s">
         <v>0</v>
       </c>
@@ -1639,20 +1774,23 @@
       <c r="D45">
         <v>-138.8637913</v>
       </c>
-      <c r="E45" s="2">
+      <c r="E45">
+        <v>2023</v>
+      </c>
+      <c r="F45" s="2">
         <v>71.194389999999999</v>
       </c>
-      <c r="F45" s="2">
+      <c r="G45" s="2">
         <v>1.1705080000000001</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>228</v>
       </c>
-      <c r="H45">
+      <c r="I45">
         <v>47.9</v>
       </c>
     </row>
-    <row r="46" spans="1:8">
+    <row r="46" spans="1:9">
       <c r="A46" t="s">
         <v>0</v>
       </c>
@@ -1665,20 +1803,23 @@
       <c r="D46">
         <v>-138.86387010000001</v>
       </c>
-      <c r="E46" s="2">
+      <c r="E46">
+        <v>2023</v>
+      </c>
+      <c r="F46" s="2">
         <v>71.170460000000006</v>
       </c>
-      <c r="F46" s="2">
+      <c r="G46" s="2">
         <v>1.1862360000000001</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>228</v>
       </c>
-      <c r="H46">
+      <c r="I46">
         <v>44.933333333333337</v>
       </c>
     </row>
-    <row r="47" spans="1:8">
+    <row r="47" spans="1:9">
       <c r="A47" t="s">
         <v>0</v>
       </c>
@@ -1691,20 +1832,23 @@
       <c r="D47">
         <v>-138.8640747</v>
       </c>
-      <c r="E47" s="2">
+      <c r="E47">
+        <v>2023</v>
+      </c>
+      <c r="F47" s="2">
         <v>71.030659999999997</v>
       </c>
-      <c r="F47" s="2">
+      <c r="G47" s="2">
         <v>1.785264</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>228</v>
       </c>
-      <c r="H47">
+      <c r="I47">
         <v>55.833333333333336</v>
       </c>
     </row>
-    <row r="48" spans="1:8">
+    <row r="48" spans="1:9">
       <c r="A48" t="s">
         <v>0</v>
       </c>
@@ -1717,20 +1861,23 @@
       <c r="D48">
         <v>-138.86817970000001</v>
       </c>
-      <c r="E48" s="2">
+      <c r="E48">
+        <v>2023</v>
+      </c>
+      <c r="F48" s="2">
         <v>71.11157</v>
       </c>
-      <c r="F48" s="2">
+      <c r="G48" s="2">
         <v>3.3767399999999999</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>228</v>
       </c>
-      <c r="H48">
+      <c r="I48">
         <v>75.100000000000009</v>
       </c>
     </row>
-    <row r="49" spans="1:8">
+    <row r="49" spans="1:9">
       <c r="A49" t="s">
         <v>0</v>
       </c>
@@ -1743,20 +1890,23 @@
       <c r="D49">
         <v>-138.86811879999999</v>
       </c>
-      <c r="E49" s="2">
+      <c r="E49">
+        <v>2023</v>
+      </c>
+      <c r="F49" s="2">
         <v>71.146529999999998</v>
       </c>
-      <c r="F49" s="2">
+      <c r="G49" s="2">
         <v>2.5742989999999999</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>228</v>
       </c>
-      <c r="H49">
+      <c r="I49">
         <v>82.066666666666677</v>
       </c>
     </row>
-    <row r="50" spans="1:8">
+    <row r="50" spans="1:9">
       <c r="A50" t="s">
         <v>0</v>
       </c>
@@ -1769,20 +1919,23 @@
       <c r="D50">
         <v>-138.86773909999999</v>
       </c>
-      <c r="E50" s="2">
+      <c r="E50">
+        <v>2023</v>
+      </c>
+      <c r="F50" s="2">
         <v>71.806269999999998</v>
       </c>
-      <c r="F50" s="2">
+      <c r="G50" s="2">
         <v>4.376296</v>
       </c>
-      <c r="G50" s="3">
+      <c r="H50" s="3">
         <v>228</v>
       </c>
-      <c r="H50">
+      <c r="I50">
         <v>91.933333333333337</v>
       </c>
     </row>
-    <row r="51" spans="1:8">
+    <row r="51" spans="1:9">
       <c r="A51" t="s">
         <v>0</v>
       </c>
@@ -1795,20 +1948,23 @@
       <c r="D51">
         <v>-138.8676384</v>
       </c>
-      <c r="E51" s="2">
+      <c r="E51">
+        <v>2023</v>
+      </c>
+      <c r="F51" s="2">
         <v>71.979259999999996</v>
       </c>
-      <c r="F51" s="2">
+      <c r="G51" s="2">
         <v>4.6941449999999998</v>
       </c>
-      <c r="G51" s="3">
+      <c r="H51" s="3">
         <v>228</v>
       </c>
-      <c r="H51">
+      <c r="I51">
         <v>98.466666666666654</v>
       </c>
     </row>
-    <row r="52" spans="1:8">
+    <row r="52" spans="1:9">
       <c r="A52" t="s">
         <v>0</v>
       </c>
@@ -1821,20 +1977,23 @@
       <c r="D52">
         <v>-138.86729539999999</v>
       </c>
-      <c r="E52" s="2">
+      <c r="E52">
+        <v>2023</v>
+      </c>
+      <c r="F52" s="2">
         <v>72.876679999999993</v>
       </c>
-      <c r="F52" s="2">
+      <c r="G52" s="2">
         <v>2.3661750000000001</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>228</v>
       </c>
-      <c r="H52">
+      <c r="I52">
         <v>78.666666666666671</v>
       </c>
     </row>
-    <row r="53" spans="1:8">
+    <row r="53" spans="1:9">
       <c r="A53" t="s">
         <v>0</v>
       </c>
@@ -1847,20 +2006,23 @@
       <c r="D53">
         <v>-138.86699780000001</v>
       </c>
-      <c r="E53" s="2">
+      <c r="E53">
+        <v>2023</v>
+      </c>
+      <c r="F53" s="2">
         <v>73.514600000000002</v>
       </c>
-      <c r="F53" s="2">
+      <c r="G53" s="2">
         <v>4.204345</v>
       </c>
-      <c r="G53" s="3">
+      <c r="H53" s="3">
         <v>228</v>
       </c>
-      <c r="H53">
+      <c r="I53">
         <v>74.133333333333326</v>
       </c>
     </row>
-    <row r="54" spans="1:8">
+    <row r="54" spans="1:9">
       <c r="A54" t="s">
         <v>0</v>
       </c>
@@ -1873,20 +2035,23 @@
       <c r="D54">
         <v>-138.91274999999999</v>
       </c>
-      <c r="E54" s="2">
+      <c r="E54">
+        <v>2023</v>
+      </c>
+      <c r="F54" s="2">
         <v>57.668939999999999</v>
       </c>
-      <c r="F54" s="2">
+      <c r="G54" s="2">
         <v>2.7936839999999998</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>228</v>
       </c>
-      <c r="H54">
+      <c r="I54">
         <v>45.70000000000001</v>
       </c>
     </row>
-    <row r="55" spans="1:8">
+    <row r="55" spans="1:9">
       <c r="A55" t="s">
         <v>0</v>
       </c>
@@ -1899,20 +2064,23 @@
       <c r="D55">
         <v>-138.91274999999999</v>
       </c>
-      <c r="E55" s="2">
+      <c r="E55">
+        <v>2023</v>
+      </c>
+      <c r="F55" s="2">
         <v>57.668939999999999</v>
       </c>
-      <c r="F55" s="2">
+      <c r="G55" s="2">
         <v>2.7936839999999998</v>
       </c>
-      <c r="G55" s="3">
+      <c r="H55" s="3">
         <v>228</v>
       </c>
-      <c r="H55">
+      <c r="I55">
         <v>50.166666666666664</v>
       </c>
     </row>
-    <row r="56" spans="1:8">
+    <row r="56" spans="1:9">
       <c r="A56" t="s">
         <v>0</v>
       </c>
@@ -1925,20 +2093,23 @@
       <c r="D56">
         <v>-138.91274999999999</v>
       </c>
-      <c r="E56" s="2">
+      <c r="E56">
+        <v>2023</v>
+      </c>
+      <c r="F56" s="2">
         <v>57.668939999999999</v>
       </c>
-      <c r="F56" s="2">
+      <c r="G56" s="2">
         <v>2.7936839999999998</v>
       </c>
-      <c r="G56" s="3">
+      <c r="H56" s="3">
         <v>228</v>
       </c>
-      <c r="H56">
+      <c r="I56">
         <v>55.133333333333333</v>
       </c>
     </row>
-    <row r="57" spans="1:8">
+    <row r="57" spans="1:9">
       <c r="A57" t="s">
         <v>0</v>
       </c>
@@ -1951,20 +2122,23 @@
       <c r="D57">
         <v>-138.91274999999999</v>
       </c>
-      <c r="E57" s="2">
+      <c r="E57">
+        <v>2023</v>
+      </c>
+      <c r="F57" s="2">
         <v>57.668939999999999</v>
       </c>
-      <c r="F57" s="2">
+      <c r="G57" s="2">
         <v>2.7936839999999998</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>228</v>
       </c>
-      <c r="H57">
+      <c r="I57">
         <v>48.43333333333333</v>
       </c>
     </row>
-    <row r="58" spans="1:8">
+    <row r="58" spans="1:9">
       <c r="A58" t="s">
         <v>0</v>
       </c>
@@ -1977,20 +2151,23 @@
       <c r="D58">
         <v>-138.90396720000001</v>
       </c>
-      <c r="E58" s="2">
+      <c r="E58">
+        <v>2023</v>
+      </c>
+      <c r="F58" s="2">
         <v>32.122779999999999</v>
       </c>
-      <c r="F58" s="2">
+      <c r="G58" s="2">
         <v>6.2787110000000004</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>228</v>
       </c>
-      <c r="H58">
+      <c r="I58">
         <v>61.79999999999999</v>
       </c>
     </row>
-    <row r="59" spans="1:8">
+    <row r="59" spans="1:9">
       <c r="A59" t="s">
         <v>0</v>
       </c>
@@ -2003,20 +2180,23 @@
       <c r="D59">
         <v>-138.90396720000001</v>
       </c>
-      <c r="E59" s="2">
+      <c r="E59">
+        <v>2023</v>
+      </c>
+      <c r="F59" s="2">
         <v>32.122779999999999</v>
       </c>
-      <c r="F59" s="2">
+      <c r="G59" s="2">
         <v>6.2787110000000004</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>228</v>
       </c>
-      <c r="H59">
+      <c r="I59">
         <v>63.866666666666674</v>
       </c>
     </row>
-    <row r="60" spans="1:8">
+    <row r="60" spans="1:9">
       <c r="A60" t="s">
         <v>0</v>
       </c>
@@ -2029,20 +2209,23 @@
       <c r="D60">
         <v>-138.90396720000001</v>
       </c>
-      <c r="E60" s="2">
+      <c r="E60">
+        <v>2023</v>
+      </c>
+      <c r="F60" s="2">
         <v>32.122779999999999</v>
       </c>
-      <c r="F60" s="2">
+      <c r="G60" s="2">
         <v>6.2787110000000004</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>228</v>
       </c>
-      <c r="H60">
+      <c r="I60">
         <v>58.833333333333336</v>
       </c>
     </row>
-    <row r="61" spans="1:8">
+    <row r="61" spans="1:9">
       <c r="A61" t="s">
         <v>0</v>
       </c>
@@ -2055,20 +2238,23 @@
       <c r="D61">
         <v>-138.90396720000001</v>
       </c>
-      <c r="E61" s="2">
+      <c r="E61">
+        <v>2023</v>
+      </c>
+      <c r="F61" s="2">
         <v>32.122779999999999</v>
       </c>
-      <c r="F61" s="2">
+      <c r="G61" s="2">
         <v>6.2787110000000004</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>228</v>
       </c>
-      <c r="H61">
+      <c r="I61">
         <v>51.766666666666673</v>
       </c>
     </row>
-    <row r="62" spans="1:8">
+    <row r="62" spans="1:9">
       <c r="A62" t="s">
         <v>0</v>
       </c>
@@ -2081,20 +2267,23 @@
       <c r="D62">
         <v>-138.90355299999999</v>
       </c>
-      <c r="E62" s="2">
+      <c r="E62">
+        <v>2023</v>
+      </c>
+      <c r="F62" s="2">
         <v>29.5139</v>
       </c>
-      <c r="F62" s="2">
+      <c r="G62" s="2">
         <v>7.6486470000000004</v>
       </c>
-      <c r="G62">
+      <c r="H62">
         <v>228</v>
       </c>
-      <c r="H62">
+      <c r="I62">
         <v>63.566666666666663</v>
       </c>
     </row>
-    <row r="63" spans="1:8">
+    <row r="63" spans="1:9">
       <c r="A63" t="s">
         <v>0</v>
       </c>
@@ -2107,20 +2296,23 @@
       <c r="D63">
         <v>-138.90355299999999</v>
       </c>
-      <c r="E63" s="2">
+      <c r="E63">
+        <v>2023</v>
+      </c>
+      <c r="F63" s="2">
         <v>29.5139</v>
       </c>
-      <c r="F63" s="2">
+      <c r="G63" s="2">
         <v>7.6486470000000004</v>
       </c>
-      <c r="G63">
+      <c r="H63">
         <v>228</v>
       </c>
-      <c r="H63">
+      <c r="I63">
         <v>51.733333333333327</v>
       </c>
     </row>
-    <row r="64" spans="1:8">
+    <row r="64" spans="1:9">
       <c r="A64" t="s">
         <v>0</v>
       </c>
@@ -2133,20 +2325,23 @@
       <c r="D64">
         <v>-138.90355299999999</v>
       </c>
-      <c r="E64" s="2">
+      <c r="E64">
+        <v>2023</v>
+      </c>
+      <c r="F64" s="2">
         <v>29.5139</v>
       </c>
-      <c r="F64" s="2">
+      <c r="G64" s="2">
         <v>7.6486470000000004</v>
       </c>
-      <c r="G64">
+      <c r="H64">
         <v>228</v>
       </c>
-      <c r="H64">
+      <c r="I64">
         <v>53.466666666666661</v>
       </c>
     </row>
-    <row r="65" spans="1:8">
+    <row r="65" spans="1:9">
       <c r="A65" t="s">
         <v>0</v>
       </c>
@@ -2159,17 +2354,4645 @@
       <c r="D65">
         <v>-138.90355299999999</v>
       </c>
-      <c r="E65" s="2">
+      <c r="E65">
+        <v>2023</v>
+      </c>
+      <c r="F65" s="2">
         <v>29.5139</v>
       </c>
-      <c r="F65" s="2">
+      <c r="G65" s="2">
         <v>7.6486470000000004</v>
       </c>
-      <c r="G65">
+      <c r="H65">
         <v>228</v>
       </c>
-      <c r="H65">
+      <c r="I65">
         <v>58.6</v>
+      </c>
+    </row>
+    <row r="66" spans="1:9">
+      <c r="A66" t="s">
+        <v>0</v>
+      </c>
+      <c r="B66" t="s">
+        <v>3</v>
+      </c>
+      <c r="C66">
+        <v>69.574881039999994</v>
+      </c>
+      <c r="D66">
+        <v>-138.86307059999999</v>
+      </c>
+      <c r="E66">
+        <v>2024</v>
+      </c>
+      <c r="F66" s="2">
+        <v>71.664990000000003</v>
+      </c>
+      <c r="G66" s="2">
+        <v>1.0686739999999999</v>
+      </c>
+      <c r="H66" s="3">
+        <v>181</v>
+      </c>
+      <c r="I66">
+        <v>48.866666666666667</v>
+      </c>
+    </row>
+    <row r="67" spans="1:9">
+      <c r="A67" t="s">
+        <v>0</v>
+      </c>
+      <c r="B67" t="s">
+        <v>3</v>
+      </c>
+      <c r="C67">
+        <v>69.574888920000006</v>
+      </c>
+      <c r="D67">
+        <v>-138.8631728</v>
+      </c>
+      <c r="E67">
+        <v>2024</v>
+      </c>
+      <c r="F67" s="2">
+        <v>71.566590000000005</v>
+      </c>
+      <c r="G67" s="2">
+        <v>3.236253</v>
+      </c>
+      <c r="H67" s="3">
+        <v>181</v>
+      </c>
+      <c r="I67">
+        <v>51.9</v>
+      </c>
+    </row>
+    <row r="68" spans="1:9">
+      <c r="A68" t="s">
+        <v>0</v>
+      </c>
+      <c r="B68" t="s">
+        <v>3</v>
+      </c>
+      <c r="C68">
+        <v>69.574882380000005</v>
+      </c>
+      <c r="D68">
+        <v>-138.8634658</v>
+      </c>
+      <c r="E68">
+        <v>2024</v>
+      </c>
+      <c r="F68" s="2">
+        <v>71.334130000000002</v>
+      </c>
+      <c r="G68" s="2">
+        <v>2.6920440000000001</v>
+      </c>
+      <c r="H68" s="3">
+        <v>181</v>
+      </c>
+      <c r="I68">
+        <v>46.866666666666667</v>
+      </c>
+    </row>
+    <row r="69" spans="1:9">
+      <c r="A69" t="s">
+        <v>0</v>
+      </c>
+      <c r="B69" t="s">
+        <v>3</v>
+      </c>
+      <c r="C69">
+        <v>69.574860330000007</v>
+      </c>
+      <c r="D69">
+        <v>-138.8637913</v>
+      </c>
+      <c r="E69">
+        <v>2024</v>
+      </c>
+      <c r="F69" s="2">
+        <v>71.194389999999999</v>
+      </c>
+      <c r="G69" s="2">
+        <v>1.1705080000000001</v>
+      </c>
+      <c r="H69" s="3">
+        <v>181</v>
+      </c>
+      <c r="I69">
+        <v>47.266666666666673</v>
+      </c>
+    </row>
+    <row r="70" spans="1:9">
+      <c r="A70" t="s">
+        <v>0</v>
+      </c>
+      <c r="B70" t="s">
+        <v>3</v>
+      </c>
+      <c r="C70">
+        <v>69.574861170000005</v>
+      </c>
+      <c r="D70">
+        <v>-138.86387010000001</v>
+      </c>
+      <c r="E70">
+        <v>2024</v>
+      </c>
+      <c r="F70" s="2">
+        <v>71.170460000000006</v>
+      </c>
+      <c r="G70" s="2">
+        <v>1.1862360000000001</v>
+      </c>
+      <c r="H70" s="3">
+        <v>181</v>
+      </c>
+      <c r="I70">
+        <v>46.4</v>
+      </c>
+    </row>
+    <row r="71" spans="1:9">
+      <c r="A71" t="s">
+        <v>0</v>
+      </c>
+      <c r="B71" t="s">
+        <v>3</v>
+      </c>
+      <c r="C71">
+        <v>69.574857399999999</v>
+      </c>
+      <c r="D71">
+        <v>-138.8640747</v>
+      </c>
+      <c r="E71">
+        <v>2024</v>
+      </c>
+      <c r="F71" s="2">
+        <v>71.030659999999997</v>
+      </c>
+      <c r="G71" s="2">
+        <v>1.785264</v>
+      </c>
+      <c r="H71" s="3">
+        <v>181</v>
+      </c>
+      <c r="I71">
+        <v>45.5</v>
+      </c>
+    </row>
+    <row r="72" spans="1:9">
+      <c r="A72" t="s">
+        <v>0</v>
+      </c>
+      <c r="B72" t="s">
+        <v>4</v>
+      </c>
+      <c r="C72">
+        <v>69.576416179999995</v>
+      </c>
+      <c r="D72">
+        <v>-138.86817970000001</v>
+      </c>
+      <c r="E72">
+        <v>2024</v>
+      </c>
+      <c r="F72" s="2">
+        <v>71.11157</v>
+      </c>
+      <c r="G72" s="2">
+        <v>3.3767399999999999</v>
+      </c>
+      <c r="H72" s="3">
+        <v>181</v>
+      </c>
+      <c r="I72">
+        <v>36.199999999999996</v>
+      </c>
+    </row>
+    <row r="73" spans="1:9">
+      <c r="A73" t="s">
+        <v>0</v>
+      </c>
+      <c r="B73" t="s">
+        <v>4</v>
+      </c>
+      <c r="C73">
+        <v>69.576403529999993</v>
+      </c>
+      <c r="D73">
+        <v>-138.86811879999999</v>
+      </c>
+      <c r="E73">
+        <v>2024</v>
+      </c>
+      <c r="F73" s="2">
+        <v>71.146529999999998</v>
+      </c>
+      <c r="G73" s="2">
+        <v>2.5742989999999999</v>
+      </c>
+      <c r="H73" s="3">
+        <v>181</v>
+      </c>
+      <c r="I73">
+        <v>23.933333333333334</v>
+      </c>
+    </row>
+    <row r="74" spans="1:9">
+      <c r="A74" t="s">
+        <v>0</v>
+      </c>
+      <c r="B74" t="s">
+        <v>4</v>
+      </c>
+      <c r="C74">
+        <v>69.576461190000003</v>
+      </c>
+      <c r="D74">
+        <v>-138.86773909999999</v>
+      </c>
+      <c r="E74">
+        <v>2024</v>
+      </c>
+      <c r="F74" s="2">
+        <v>71.806269999999998</v>
+      </c>
+      <c r="G74" s="2">
+        <v>4.376296</v>
+      </c>
+      <c r="H74" s="3">
+        <v>181</v>
+      </c>
+      <c r="I74">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="75" spans="1:9">
+      <c r="A75" t="s">
+        <v>0</v>
+      </c>
+      <c r="B75" t="s">
+        <v>4</v>
+      </c>
+      <c r="C75">
+        <v>69.576468489999996</v>
+      </c>
+      <c r="D75">
+        <v>-138.8676384</v>
+      </c>
+      <c r="E75">
+        <v>2024</v>
+      </c>
+      <c r="F75" s="2">
+        <v>71.979259999999996</v>
+      </c>
+      <c r="G75" s="2">
+        <v>4.6941449999999998</v>
+      </c>
+      <c r="H75" s="3">
+        <v>181</v>
+      </c>
+      <c r="I75">
+        <v>25.066666666666666</v>
+      </c>
+    </row>
+    <row r="76" spans="1:9">
+      <c r="A76" t="s">
+        <v>0</v>
+      </c>
+      <c r="B76" t="s">
+        <v>4</v>
+      </c>
+      <c r="C76">
+        <v>69.576505789999999</v>
+      </c>
+      <c r="D76">
+        <v>-138.86729539999999</v>
+      </c>
+      <c r="E76">
+        <v>2024</v>
+      </c>
+      <c r="F76" s="2">
+        <v>72.876679999999993</v>
+      </c>
+      <c r="G76" s="2">
+        <v>2.3661750000000001</v>
+      </c>
+      <c r="H76" s="3">
+        <v>181</v>
+      </c>
+      <c r="I76">
+        <v>19.766666666666666</v>
+      </c>
+    </row>
+    <row r="77" spans="1:9">
+      <c r="A77" t="s">
+        <v>0</v>
+      </c>
+      <c r="B77" t="s">
+        <v>4</v>
+      </c>
+      <c r="C77">
+        <v>69.576544850000005</v>
+      </c>
+      <c r="D77">
+        <v>-138.86699780000001</v>
+      </c>
+      <c r="E77">
+        <v>2024</v>
+      </c>
+      <c r="F77" s="2">
+        <v>73.514600000000002</v>
+      </c>
+      <c r="G77" s="2">
+        <v>4.204345</v>
+      </c>
+      <c r="H77" s="3">
+        <v>181</v>
+      </c>
+      <c r="I77">
+        <v>36.366666666666667</v>
+      </c>
+    </row>
+    <row r="78" spans="1:9">
+      <c r="A78" t="s">
+        <v>0</v>
+      </c>
+      <c r="B78" t="s">
+        <v>5</v>
+      </c>
+      <c r="C78">
+        <v>69.577619990000002</v>
+      </c>
+      <c r="D78">
+        <v>-138.91274999999999</v>
+      </c>
+      <c r="E78">
+        <v>2024</v>
+      </c>
+      <c r="F78" s="2">
+        <v>57.668939999999999</v>
+      </c>
+      <c r="G78" s="2">
+        <v>2.7936839999999998</v>
+      </c>
+      <c r="H78" s="3">
+        <v>180</v>
+      </c>
+      <c r="I78">
+        <v>12.733333333333334</v>
+      </c>
+    </row>
+    <row r="79" spans="1:9">
+      <c r="A79" t="s">
+        <v>0</v>
+      </c>
+      <c r="B79" t="s">
+        <v>5</v>
+      </c>
+      <c r="C79">
+        <v>69.577619990000002</v>
+      </c>
+      <c r="D79">
+        <v>-138.91274999999999</v>
+      </c>
+      <c r="E79">
+        <v>2024</v>
+      </c>
+      <c r="F79" s="2">
+        <v>57.668939999999999</v>
+      </c>
+      <c r="G79" s="2">
+        <v>2.7936839999999998</v>
+      </c>
+      <c r="H79" s="3">
+        <v>180</v>
+      </c>
+      <c r="I79">
+        <v>14.333333333333334</v>
+      </c>
+    </row>
+    <row r="80" spans="1:9">
+      <c r="A80" t="s">
+        <v>0</v>
+      </c>
+      <c r="B80" t="s">
+        <v>5</v>
+      </c>
+      <c r="C80">
+        <v>69.577619990000002</v>
+      </c>
+      <c r="D80">
+        <v>-138.91274999999999</v>
+      </c>
+      <c r="E80">
+        <v>2024</v>
+      </c>
+      <c r="F80" s="2">
+        <v>57.668939999999999</v>
+      </c>
+      <c r="G80" s="2">
+        <v>2.7936839999999998</v>
+      </c>
+      <c r="H80" s="3">
+        <v>180</v>
+      </c>
+      <c r="I80">
+        <v>14.166666666666666</v>
+      </c>
+    </row>
+    <row r="81" spans="1:9">
+      <c r="A81" t="s">
+        <v>0</v>
+      </c>
+      <c r="B81" t="s">
+        <v>5</v>
+      </c>
+      <c r="C81">
+        <v>69.577619990000002</v>
+      </c>
+      <c r="D81">
+        <v>-138.91274999999999</v>
+      </c>
+      <c r="E81">
+        <v>2024</v>
+      </c>
+      <c r="F81" s="2">
+        <v>57.668939999999999</v>
+      </c>
+      <c r="G81" s="2">
+        <v>2.7936839999999998</v>
+      </c>
+      <c r="H81" s="3">
+        <v>180</v>
+      </c>
+      <c r="I81">
+        <v>11.033333333333333</v>
+      </c>
+    </row>
+    <row r="82" spans="1:9">
+      <c r="A82" t="s">
+        <v>0</v>
+      </c>
+      <c r="B82" t="s">
+        <v>5</v>
+      </c>
+      <c r="C82">
+        <v>69.577619990000002</v>
+      </c>
+      <c r="D82">
+        <v>-138.91274999999999</v>
+      </c>
+      <c r="E82">
+        <v>2024</v>
+      </c>
+      <c r="F82" s="2">
+        <v>57.668939999999999</v>
+      </c>
+      <c r="G82" s="2">
+        <v>2.7936839999999998</v>
+      </c>
+      <c r="H82" s="3">
+        <v>180</v>
+      </c>
+      <c r="I82">
+        <v>8.2666666666666675</v>
+      </c>
+    </row>
+    <row r="83" spans="1:9">
+      <c r="A83" t="s">
+        <v>0</v>
+      </c>
+      <c r="B83" t="s">
+        <v>6</v>
+      </c>
+      <c r="C83">
+        <v>69.575540020000005</v>
+      </c>
+      <c r="D83">
+        <v>-138.90445</v>
+      </c>
+      <c r="E83">
+        <v>2024</v>
+      </c>
+      <c r="F83" s="2">
+        <v>28.906300000000002</v>
+      </c>
+      <c r="G83" s="2">
+        <v>4.0111990000000004</v>
+      </c>
+      <c r="H83" s="3">
+        <v>180</v>
+      </c>
+      <c r="I83">
+        <v>6.666666666666667</v>
+      </c>
+    </row>
+    <row r="84" spans="1:9">
+      <c r="A84" t="s">
+        <v>0</v>
+      </c>
+      <c r="B84" t="s">
+        <v>6</v>
+      </c>
+      <c r="C84">
+        <v>69.575540020000005</v>
+      </c>
+      <c r="D84">
+        <v>-138.90445</v>
+      </c>
+      <c r="E84">
+        <v>2024</v>
+      </c>
+      <c r="F84" s="2">
+        <v>28.906300000000002</v>
+      </c>
+      <c r="G84" s="2">
+        <v>4.0111990000000004</v>
+      </c>
+      <c r="H84" s="3">
+        <v>180</v>
+      </c>
+      <c r="I84">
+        <v>7.1333333333333329</v>
+      </c>
+    </row>
+    <row r="85" spans="1:9">
+      <c r="A85" t="s">
+        <v>0</v>
+      </c>
+      <c r="B85" t="s">
+        <v>6</v>
+      </c>
+      <c r="C85">
+        <v>69.575540020000005</v>
+      </c>
+      <c r="D85">
+        <v>-138.90445</v>
+      </c>
+      <c r="E85">
+        <v>2024</v>
+      </c>
+      <c r="F85" s="2">
+        <v>28.906300000000002</v>
+      </c>
+      <c r="G85" s="2">
+        <v>4.0111990000000004</v>
+      </c>
+      <c r="H85" s="3">
+        <v>180</v>
+      </c>
+      <c r="I85">
+        <v>11.133333333333333</v>
+      </c>
+    </row>
+    <row r="86" spans="1:9">
+      <c r="A86" t="s">
+        <v>0</v>
+      </c>
+      <c r="B86" t="s">
+        <v>6</v>
+      </c>
+      <c r="C86">
+        <v>69.575540020000005</v>
+      </c>
+      <c r="D86">
+        <v>-138.90445</v>
+      </c>
+      <c r="E86">
+        <v>2024</v>
+      </c>
+      <c r="F86" s="2">
+        <v>28.906300000000002</v>
+      </c>
+      <c r="G86" s="2">
+        <v>4.0111990000000004</v>
+      </c>
+      <c r="H86" s="3">
+        <v>180</v>
+      </c>
+      <c r="I86">
+        <v>8.3333333333333339</v>
+      </c>
+    </row>
+    <row r="87" spans="1:9">
+      <c r="A87" t="s">
+        <v>0</v>
+      </c>
+      <c r="B87" t="s">
+        <v>6</v>
+      </c>
+      <c r="C87">
+        <v>69.575540020000005</v>
+      </c>
+      <c r="D87">
+        <v>-138.90445</v>
+      </c>
+      <c r="E87">
+        <v>2024</v>
+      </c>
+      <c r="F87" s="2">
+        <v>28.906300000000002</v>
+      </c>
+      <c r="G87" s="2">
+        <v>4.0111990000000004</v>
+      </c>
+      <c r="H87" s="3">
+        <v>180</v>
+      </c>
+      <c r="I87">
+        <v>10.466666666666667</v>
+      </c>
+    </row>
+    <row r="88" spans="1:9">
+      <c r="A88" t="s">
+        <v>0</v>
+      </c>
+      <c r="B88" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C88">
+        <v>69.576106809999999</v>
+      </c>
+      <c r="D88">
+        <v>-138.90396720000001</v>
+      </c>
+      <c r="E88">
+        <v>2024</v>
+      </c>
+      <c r="F88" s="2">
+        <v>32.122779999999999</v>
+      </c>
+      <c r="G88" s="2">
+        <v>6.2787110000000004</v>
+      </c>
+      <c r="H88" s="3">
+        <v>180</v>
+      </c>
+      <c r="I88">
+        <v>13.066666666666668</v>
+      </c>
+    </row>
+    <row r="89" spans="1:9">
+      <c r="A89" t="s">
+        <v>0</v>
+      </c>
+      <c r="B89" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C89">
+        <v>69.576106809999999</v>
+      </c>
+      <c r="D89">
+        <v>-138.90396720000001</v>
+      </c>
+      <c r="E89">
+        <v>2024</v>
+      </c>
+      <c r="F89" s="2">
+        <v>32.122779999999999</v>
+      </c>
+      <c r="G89" s="2">
+        <v>6.2787110000000004</v>
+      </c>
+      <c r="H89" s="3">
+        <v>180</v>
+      </c>
+      <c r="I89">
+        <v>21.033333333333335</v>
+      </c>
+    </row>
+    <row r="90" spans="1:9">
+      <c r="A90" t="s">
+        <v>0</v>
+      </c>
+      <c r="B90" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C90">
+        <v>69.576106809999999</v>
+      </c>
+      <c r="D90">
+        <v>-138.90396720000001</v>
+      </c>
+      <c r="E90">
+        <v>2024</v>
+      </c>
+      <c r="F90" s="2">
+        <v>32.122779999999999</v>
+      </c>
+      <c r="G90" s="2">
+        <v>6.2787110000000004</v>
+      </c>
+      <c r="H90" s="3">
+        <v>180</v>
+      </c>
+      <c r="I90">
+        <v>19.3</v>
+      </c>
+    </row>
+    <row r="91" spans="1:9">
+      <c r="A91" t="s">
+        <v>0</v>
+      </c>
+      <c r="B91" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C91">
+        <v>69.576106809999999</v>
+      </c>
+      <c r="D91">
+        <v>-138.90396720000001</v>
+      </c>
+      <c r="E91">
+        <v>2024</v>
+      </c>
+      <c r="F91" s="2">
+        <v>32.122779999999999</v>
+      </c>
+      <c r="G91" s="2">
+        <v>6.2787110000000004</v>
+      </c>
+      <c r="H91" s="3">
+        <v>180</v>
+      </c>
+      <c r="I91">
+        <v>15.133333333333335</v>
+      </c>
+    </row>
+    <row r="92" spans="1:9">
+      <c r="A92" t="s">
+        <v>0</v>
+      </c>
+      <c r="B92" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C92">
+        <v>69.576106809999999</v>
+      </c>
+      <c r="D92">
+        <v>-138.90396720000001</v>
+      </c>
+      <c r="E92">
+        <v>2024</v>
+      </c>
+      <c r="F92" s="2">
+        <v>32.122779999999999</v>
+      </c>
+      <c r="G92" s="2">
+        <v>6.2787110000000004</v>
+      </c>
+      <c r="H92" s="3">
+        <v>180</v>
+      </c>
+      <c r="I92">
+        <v>11.166666666666666</v>
+      </c>
+    </row>
+    <row r="93" spans="1:9">
+      <c r="A93" t="s">
+        <v>0</v>
+      </c>
+      <c r="B93" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C93">
+        <v>69.575888039999995</v>
+      </c>
+      <c r="D93">
+        <v>-138.90355299999999</v>
+      </c>
+      <c r="E93">
+        <v>2024</v>
+      </c>
+      <c r="F93" s="2">
+        <v>29.5139</v>
+      </c>
+      <c r="G93" s="2">
+        <v>7.6486470000000004</v>
+      </c>
+      <c r="H93" s="3">
+        <v>180</v>
+      </c>
+      <c r="I93">
+        <v>23.433333333333334</v>
+      </c>
+    </row>
+    <row r="94" spans="1:9">
+      <c r="A94" t="s">
+        <v>0</v>
+      </c>
+      <c r="B94" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C94">
+        <v>69.575888039999995</v>
+      </c>
+      <c r="D94">
+        <v>-138.90355299999999</v>
+      </c>
+      <c r="E94">
+        <v>2024</v>
+      </c>
+      <c r="F94" s="2">
+        <v>29.5139</v>
+      </c>
+      <c r="G94" s="2">
+        <v>7.6486470000000004</v>
+      </c>
+      <c r="H94" s="3">
+        <v>180</v>
+      </c>
+      <c r="I94">
+        <v>18.266666666666669</v>
+      </c>
+    </row>
+    <row r="95" spans="1:9">
+      <c r="A95" t="s">
+        <v>0</v>
+      </c>
+      <c r="B95" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C95">
+        <v>69.575888039999995</v>
+      </c>
+      <c r="D95">
+        <v>-138.90355299999999</v>
+      </c>
+      <c r="E95">
+        <v>2024</v>
+      </c>
+      <c r="F95" s="2">
+        <v>29.5139</v>
+      </c>
+      <c r="G95" s="2">
+        <v>7.6486470000000004</v>
+      </c>
+      <c r="H95" s="3">
+        <v>180</v>
+      </c>
+      <c r="I95">
+        <v>15.766666666666667</v>
+      </c>
+    </row>
+    <row r="96" spans="1:9">
+      <c r="A96" t="s">
+        <v>0</v>
+      </c>
+      <c r="B96" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C96">
+        <v>69.575888039999995</v>
+      </c>
+      <c r="D96">
+        <v>-138.90355299999999</v>
+      </c>
+      <c r="E96">
+        <v>2024</v>
+      </c>
+      <c r="F96" s="2">
+        <v>29.5139</v>
+      </c>
+      <c r="G96" s="2">
+        <v>7.6486470000000004</v>
+      </c>
+      <c r="H96" s="3">
+        <v>180</v>
+      </c>
+      <c r="I96">
+        <v>17.666666666666668</v>
+      </c>
+    </row>
+    <row r="97" spans="1:9">
+      <c r="A97" t="s">
+        <v>0</v>
+      </c>
+      <c r="B97" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C97">
+        <v>69.575888039999995</v>
+      </c>
+      <c r="D97">
+        <v>-138.90355299999999</v>
+      </c>
+      <c r="E97">
+        <v>2024</v>
+      </c>
+      <c r="F97" s="2">
+        <v>29.5139</v>
+      </c>
+      <c r="G97" s="2">
+        <v>7.6486470000000004</v>
+      </c>
+      <c r="H97" s="3">
+        <v>180</v>
+      </c>
+      <c r="I97">
+        <v>16.233333333333334</v>
+      </c>
+    </row>
+    <row r="98" spans="1:9">
+      <c r="A98" t="s">
+        <v>0</v>
+      </c>
+      <c r="B98" t="s">
+        <v>5</v>
+      </c>
+      <c r="C98">
+        <v>69.577619990000002</v>
+      </c>
+      <c r="D98">
+        <v>-138.91274999999999</v>
+      </c>
+      <c r="E98">
+        <v>2024</v>
+      </c>
+      <c r="F98" s="2">
+        <v>57.668939999999999</v>
+      </c>
+      <c r="G98" s="2">
+        <v>2.7936839999999998</v>
+      </c>
+      <c r="H98" s="3">
+        <v>187</v>
+      </c>
+      <c r="I98">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="99" spans="1:9">
+      <c r="A99" t="s">
+        <v>0</v>
+      </c>
+      <c r="B99" t="s">
+        <v>5</v>
+      </c>
+      <c r="C99">
+        <v>69.577619990000002</v>
+      </c>
+      <c r="D99">
+        <v>-138.91274999999999</v>
+      </c>
+      <c r="E99">
+        <v>2024</v>
+      </c>
+      <c r="F99" s="2">
+        <v>57.668939999999999</v>
+      </c>
+      <c r="G99" s="2">
+        <v>2.7936839999999998</v>
+      </c>
+      <c r="H99" s="3">
+        <v>187</v>
+      </c>
+      <c r="I99">
+        <v>31.166666666666668</v>
+      </c>
+    </row>
+    <row r="100" spans="1:9">
+      <c r="A100" t="s">
+        <v>0</v>
+      </c>
+      <c r="B100" t="s">
+        <v>5</v>
+      </c>
+      <c r="C100">
+        <v>69.577619990000002</v>
+      </c>
+      <c r="D100">
+        <v>-138.91274999999999</v>
+      </c>
+      <c r="E100">
+        <v>2024</v>
+      </c>
+      <c r="F100" s="2">
+        <v>57.668939999999999</v>
+      </c>
+      <c r="G100" s="2">
+        <v>2.7936839999999998</v>
+      </c>
+      <c r="H100" s="3">
+        <v>187</v>
+      </c>
+      <c r="I100">
+        <v>26.899999999999995</v>
+      </c>
+    </row>
+    <row r="101" spans="1:9">
+      <c r="A101" t="s">
+        <v>0</v>
+      </c>
+      <c r="B101" t="s">
+        <v>5</v>
+      </c>
+      <c r="C101">
+        <v>69.577619990000002</v>
+      </c>
+      <c r="D101">
+        <v>-138.91274999999999</v>
+      </c>
+      <c r="E101">
+        <v>2024</v>
+      </c>
+      <c r="F101" s="2">
+        <v>57.668939999999999</v>
+      </c>
+      <c r="G101" s="2">
+        <v>2.7936839999999998</v>
+      </c>
+      <c r="H101" s="3">
+        <v>187</v>
+      </c>
+      <c r="I101">
+        <v>24.033333333333331</v>
+      </c>
+    </row>
+    <row r="102" spans="1:9">
+      <c r="A102" t="s">
+        <v>0</v>
+      </c>
+      <c r="B102" t="s">
+        <v>5</v>
+      </c>
+      <c r="C102">
+        <v>69.577619990000002</v>
+      </c>
+      <c r="D102">
+        <v>-138.91274999999999</v>
+      </c>
+      <c r="E102">
+        <v>2024</v>
+      </c>
+      <c r="F102" s="2">
+        <v>57.668939999999999</v>
+      </c>
+      <c r="G102" s="2">
+        <v>2.7936839999999998</v>
+      </c>
+      <c r="H102" s="3">
+        <v>187</v>
+      </c>
+      <c r="I102">
+        <v>20.266666666666666</v>
+      </c>
+    </row>
+    <row r="103" spans="1:9">
+      <c r="A103" t="s">
+        <v>0</v>
+      </c>
+      <c r="B103" t="s">
+        <v>6</v>
+      </c>
+      <c r="C103">
+        <v>69.575540020000005</v>
+      </c>
+      <c r="D103">
+        <v>-138.90445</v>
+      </c>
+      <c r="E103">
+        <v>2024</v>
+      </c>
+      <c r="F103" s="2">
+        <v>28.906300000000002</v>
+      </c>
+      <c r="G103" s="2">
+        <v>4.0111990000000004</v>
+      </c>
+      <c r="H103" s="3">
+        <v>187</v>
+      </c>
+      <c r="I103">
+        <v>32.300000000000004</v>
+      </c>
+    </row>
+    <row r="104" spans="1:9">
+      <c r="A104" t="s">
+        <v>0</v>
+      </c>
+      <c r="B104" t="s">
+        <v>6</v>
+      </c>
+      <c r="C104">
+        <v>69.575540020000005</v>
+      </c>
+      <c r="D104">
+        <v>-138.90445</v>
+      </c>
+      <c r="E104">
+        <v>2024</v>
+      </c>
+      <c r="F104" s="2">
+        <v>28.906300000000002</v>
+      </c>
+      <c r="G104" s="2">
+        <v>4.0111990000000004</v>
+      </c>
+      <c r="H104" s="3">
+        <v>187</v>
+      </c>
+      <c r="I104">
+        <v>29.066666666666666</v>
+      </c>
+    </row>
+    <row r="105" spans="1:9">
+      <c r="A105" t="s">
+        <v>0</v>
+      </c>
+      <c r="B105" t="s">
+        <v>6</v>
+      </c>
+      <c r="C105">
+        <v>69.575540020000005</v>
+      </c>
+      <c r="D105">
+        <v>-138.90445</v>
+      </c>
+      <c r="E105">
+        <v>2024</v>
+      </c>
+      <c r="F105" s="2">
+        <v>28.906300000000002</v>
+      </c>
+      <c r="G105" s="2">
+        <v>4.0111990000000004</v>
+      </c>
+      <c r="H105" s="3">
+        <v>187</v>
+      </c>
+      <c r="I105">
+        <v>24.733333333333334</v>
+      </c>
+    </row>
+    <row r="106" spans="1:9">
+      <c r="A106" t="s">
+        <v>0</v>
+      </c>
+      <c r="B106" t="s">
+        <v>6</v>
+      </c>
+      <c r="C106">
+        <v>69.575540020000005</v>
+      </c>
+      <c r="D106">
+        <v>-138.90445</v>
+      </c>
+      <c r="E106">
+        <v>2024</v>
+      </c>
+      <c r="F106" s="2">
+        <v>28.906300000000002</v>
+      </c>
+      <c r="G106" s="2">
+        <v>4.0111990000000004</v>
+      </c>
+      <c r="H106" s="3">
+        <v>187</v>
+      </c>
+      <c r="I106">
+        <v>25.966666666666669</v>
+      </c>
+    </row>
+    <row r="107" spans="1:9">
+      <c r="A107" t="s">
+        <v>0</v>
+      </c>
+      <c r="B107" t="s">
+        <v>6</v>
+      </c>
+      <c r="C107">
+        <v>69.575540020000005</v>
+      </c>
+      <c r="D107">
+        <v>-138.90445</v>
+      </c>
+      <c r="E107">
+        <v>2024</v>
+      </c>
+      <c r="F107" s="2">
+        <v>28.906300000000002</v>
+      </c>
+      <c r="G107" s="2">
+        <v>4.0111990000000004</v>
+      </c>
+      <c r="H107" s="3">
+        <v>187</v>
+      </c>
+      <c r="I107">
+        <v>25.866666666666664</v>
+      </c>
+    </row>
+    <row r="108" spans="1:9">
+      <c r="A108" t="s">
+        <v>0</v>
+      </c>
+      <c r="B108" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C108">
+        <v>69.576106809999999</v>
+      </c>
+      <c r="D108">
+        <v>-138.90396720000001</v>
+      </c>
+      <c r="E108">
+        <v>2024</v>
+      </c>
+      <c r="F108" s="2">
+        <v>32.122779999999999</v>
+      </c>
+      <c r="G108" s="2">
+        <v>6.2787110000000004</v>
+      </c>
+      <c r="H108" s="3">
+        <v>187</v>
+      </c>
+      <c r="I108">
+        <v>28.333333333333332</v>
+      </c>
+    </row>
+    <row r="109" spans="1:9">
+      <c r="A109" t="s">
+        <v>0</v>
+      </c>
+      <c r="B109" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C109">
+        <v>69.576106809999999</v>
+      </c>
+      <c r="D109">
+        <v>-138.90396720000001</v>
+      </c>
+      <c r="E109">
+        <v>2024</v>
+      </c>
+      <c r="F109" s="2">
+        <v>32.122779999999999</v>
+      </c>
+      <c r="G109" s="2">
+        <v>6.2787110000000004</v>
+      </c>
+      <c r="H109" s="3">
+        <v>187</v>
+      </c>
+      <c r="I109">
+        <v>35.56666666666667</v>
+      </c>
+    </row>
+    <row r="110" spans="1:9">
+      <c r="A110" t="s">
+        <v>0</v>
+      </c>
+      <c r="B110" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C110">
+        <v>69.576106809999999</v>
+      </c>
+      <c r="D110">
+        <v>-138.90396720000001</v>
+      </c>
+      <c r="E110">
+        <v>2024</v>
+      </c>
+      <c r="F110" s="2">
+        <v>32.122779999999999</v>
+      </c>
+      <c r="G110" s="2">
+        <v>6.2787110000000004</v>
+      </c>
+      <c r="H110" s="3">
+        <v>187</v>
+      </c>
+      <c r="I110">
+        <v>29.533333333333331</v>
+      </c>
+    </row>
+    <row r="111" spans="1:9">
+      <c r="A111" t="s">
+        <v>0</v>
+      </c>
+      <c r="B111" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C111">
+        <v>69.576106809999999</v>
+      </c>
+      <c r="D111">
+        <v>-138.90396720000001</v>
+      </c>
+      <c r="E111">
+        <v>2024</v>
+      </c>
+      <c r="F111" s="2">
+        <v>32.122779999999999</v>
+      </c>
+      <c r="G111" s="2">
+        <v>6.2787110000000004</v>
+      </c>
+      <c r="H111" s="3">
+        <v>187</v>
+      </c>
+      <c r="I111">
+        <v>24.8</v>
+      </c>
+    </row>
+    <row r="112" spans="1:9">
+      <c r="A112" t="s">
+        <v>0</v>
+      </c>
+      <c r="B112" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C112">
+        <v>69.576106809999999</v>
+      </c>
+      <c r="D112">
+        <v>-138.90396720000001</v>
+      </c>
+      <c r="E112">
+        <v>2024</v>
+      </c>
+      <c r="F112" s="2">
+        <v>32.122779999999999</v>
+      </c>
+      <c r="G112" s="2">
+        <v>6.2787110000000004</v>
+      </c>
+      <c r="H112" s="3">
+        <v>187</v>
+      </c>
+      <c r="I112">
+        <v>24.466666666666669</v>
+      </c>
+    </row>
+    <row r="113" spans="1:9">
+      <c r="A113" t="s">
+        <v>0</v>
+      </c>
+      <c r="B113" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C113">
+        <v>69.575888039999995</v>
+      </c>
+      <c r="D113">
+        <v>-138.90355299999999</v>
+      </c>
+      <c r="E113">
+        <v>2024</v>
+      </c>
+      <c r="F113" s="2">
+        <v>29.5139</v>
+      </c>
+      <c r="G113" s="2">
+        <v>7.6486470000000004</v>
+      </c>
+      <c r="H113" s="3">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="114" spans="1:9">
+      <c r="A114" t="s">
+        <v>0</v>
+      </c>
+      <c r="B114" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C114">
+        <v>69.575888039999995</v>
+      </c>
+      <c r="D114">
+        <v>-138.90355299999999</v>
+      </c>
+      <c r="E114">
+        <v>2024</v>
+      </c>
+      <c r="F114" s="2">
+        <v>29.5139</v>
+      </c>
+      <c r="G114" s="2">
+        <v>7.6486470000000004</v>
+      </c>
+      <c r="H114" s="3">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="115" spans="1:9">
+      <c r="A115" t="s">
+        <v>0</v>
+      </c>
+      <c r="B115" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C115">
+        <v>69.575888039999995</v>
+      </c>
+      <c r="D115">
+        <v>-138.90355299999999</v>
+      </c>
+      <c r="E115">
+        <v>2024</v>
+      </c>
+      <c r="F115" s="2">
+        <v>29.5139</v>
+      </c>
+      <c r="G115" s="2">
+        <v>7.6486470000000004</v>
+      </c>
+      <c r="H115" s="3">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="116" spans="1:9">
+      <c r="A116" t="s">
+        <v>0</v>
+      </c>
+      <c r="B116" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C116">
+        <v>69.575888039999995</v>
+      </c>
+      <c r="D116">
+        <v>-138.90355299999999</v>
+      </c>
+      <c r="E116">
+        <v>2024</v>
+      </c>
+      <c r="F116" s="2">
+        <v>29.5139</v>
+      </c>
+      <c r="G116" s="2">
+        <v>7.6486470000000004</v>
+      </c>
+      <c r="H116" s="3">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="117" spans="1:9">
+      <c r="A117" t="s">
+        <v>0</v>
+      </c>
+      <c r="B117" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C117">
+        <v>69.575888039999995</v>
+      </c>
+      <c r="D117">
+        <v>-138.90355299999999</v>
+      </c>
+      <c r="E117">
+        <v>2024</v>
+      </c>
+      <c r="F117" s="2">
+        <v>29.5139</v>
+      </c>
+      <c r="G117" s="2">
+        <v>7.6486470000000004</v>
+      </c>
+      <c r="H117" s="3">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="118" spans="1:9">
+      <c r="A118" t="s">
+        <v>0</v>
+      </c>
+      <c r="B118" t="s">
+        <v>3</v>
+      </c>
+      <c r="C118">
+        <v>69.574881039999994</v>
+      </c>
+      <c r="D118">
+        <v>-138.86307059999999</v>
+      </c>
+      <c r="E118">
+        <v>2024</v>
+      </c>
+      <c r="F118" s="2">
+        <v>71.664990000000003</v>
+      </c>
+      <c r="G118" s="2">
+        <v>1.0686739999999999</v>
+      </c>
+      <c r="H118" s="3">
+        <v>191</v>
+      </c>
+      <c r="I118">
+        <v>48.866666666666667</v>
+      </c>
+    </row>
+    <row r="119" spans="1:9">
+      <c r="A119" t="s">
+        <v>0</v>
+      </c>
+      <c r="B119" t="s">
+        <v>3</v>
+      </c>
+      <c r="C119">
+        <v>69.574888920000006</v>
+      </c>
+      <c r="D119">
+        <v>-138.8631728</v>
+      </c>
+      <c r="E119">
+        <v>2024</v>
+      </c>
+      <c r="F119" s="2">
+        <v>71.566590000000005</v>
+      </c>
+      <c r="G119" s="2">
+        <v>3.236253</v>
+      </c>
+      <c r="H119" s="3">
+        <v>191</v>
+      </c>
+      <c r="I119">
+        <v>51.9</v>
+      </c>
+    </row>
+    <row r="120" spans="1:9">
+      <c r="A120" t="s">
+        <v>0</v>
+      </c>
+      <c r="B120" t="s">
+        <v>3</v>
+      </c>
+      <c r="C120">
+        <v>69.574882380000005</v>
+      </c>
+      <c r="D120">
+        <v>-138.8634658</v>
+      </c>
+      <c r="E120">
+        <v>2024</v>
+      </c>
+      <c r="F120" s="2">
+        <v>71.334130000000002</v>
+      </c>
+      <c r="G120" s="2">
+        <v>2.6920440000000001</v>
+      </c>
+      <c r="H120" s="3">
+        <v>191</v>
+      </c>
+      <c r="I120">
+        <v>46.866666666666667</v>
+      </c>
+    </row>
+    <row r="121" spans="1:9">
+      <c r="A121" t="s">
+        <v>0</v>
+      </c>
+      <c r="B121" t="s">
+        <v>3</v>
+      </c>
+      <c r="C121">
+        <v>69.574860330000007</v>
+      </c>
+      <c r="D121">
+        <v>-138.8637913</v>
+      </c>
+      <c r="E121">
+        <v>2024</v>
+      </c>
+      <c r="F121" s="2">
+        <v>71.194389999999999</v>
+      </c>
+      <c r="G121" s="2">
+        <v>1.1705080000000001</v>
+      </c>
+      <c r="H121" s="3">
+        <v>191</v>
+      </c>
+      <c r="I121">
+        <v>47.266666666666673</v>
+      </c>
+    </row>
+    <row r="122" spans="1:9">
+      <c r="A122" t="s">
+        <v>0</v>
+      </c>
+      <c r="B122" t="s">
+        <v>3</v>
+      </c>
+      <c r="C122">
+        <v>69.574861170000005</v>
+      </c>
+      <c r="D122">
+        <v>-138.86387010000001</v>
+      </c>
+      <c r="E122">
+        <v>2024</v>
+      </c>
+      <c r="F122" s="2">
+        <v>71.170460000000006</v>
+      </c>
+      <c r="G122" s="2">
+        <v>1.1862360000000001</v>
+      </c>
+      <c r="H122" s="3">
+        <v>191</v>
+      </c>
+      <c r="I122">
+        <v>46.4</v>
+      </c>
+    </row>
+    <row r="123" spans="1:9">
+      <c r="A123" t="s">
+        <v>0</v>
+      </c>
+      <c r="B123" t="s">
+        <v>3</v>
+      </c>
+      <c r="C123">
+        <v>69.574857399999999</v>
+      </c>
+      <c r="D123">
+        <v>-138.8640747</v>
+      </c>
+      <c r="E123">
+        <v>2024</v>
+      </c>
+      <c r="F123" s="2">
+        <v>71.030659999999997</v>
+      </c>
+      <c r="G123" s="2">
+        <v>1.785264</v>
+      </c>
+      <c r="H123" s="3">
+        <v>191</v>
+      </c>
+      <c r="I123">
+        <v>45.5</v>
+      </c>
+    </row>
+    <row r="124" spans="1:9">
+      <c r="A124" t="s">
+        <v>0</v>
+      </c>
+      <c r="B124" t="s">
+        <v>4</v>
+      </c>
+      <c r="C124">
+        <v>69.576416179999995</v>
+      </c>
+      <c r="D124">
+        <v>-138.86817970000001</v>
+      </c>
+      <c r="E124">
+        <v>2024</v>
+      </c>
+      <c r="F124" s="2">
+        <v>71.11157</v>
+      </c>
+      <c r="G124" s="2">
+        <v>3.3767399999999999</v>
+      </c>
+      <c r="H124" s="3">
+        <v>191</v>
+      </c>
+      <c r="I124">
+        <v>36.199999999999996</v>
+      </c>
+    </row>
+    <row r="125" spans="1:9">
+      <c r="A125" t="s">
+        <v>0</v>
+      </c>
+      <c r="B125" t="s">
+        <v>4</v>
+      </c>
+      <c r="C125">
+        <v>69.576403529999993</v>
+      </c>
+      <c r="D125">
+        <v>-138.86811879999999</v>
+      </c>
+      <c r="E125">
+        <v>2024</v>
+      </c>
+      <c r="F125" s="2">
+        <v>71.146529999999998</v>
+      </c>
+      <c r="G125" s="2">
+        <v>2.5742989999999999</v>
+      </c>
+      <c r="H125" s="3">
+        <v>191</v>
+      </c>
+      <c r="I125">
+        <v>23.933333333333334</v>
+      </c>
+    </row>
+    <row r="126" spans="1:9">
+      <c r="A126" t="s">
+        <v>0</v>
+      </c>
+      <c r="B126" t="s">
+        <v>4</v>
+      </c>
+      <c r="C126">
+        <v>69.576461190000003</v>
+      </c>
+      <c r="D126">
+        <v>-138.86773909999999</v>
+      </c>
+      <c r="E126">
+        <v>2024</v>
+      </c>
+      <c r="F126" s="2">
+        <v>71.806269999999998</v>
+      </c>
+      <c r="G126" s="2">
+        <v>4.376296</v>
+      </c>
+      <c r="H126" s="3">
+        <v>191</v>
+      </c>
+      <c r="I126">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="127" spans="1:9">
+      <c r="A127" t="s">
+        <v>0</v>
+      </c>
+      <c r="B127" t="s">
+        <v>4</v>
+      </c>
+      <c r="C127">
+        <v>69.576468489999996</v>
+      </c>
+      <c r="D127">
+        <v>-138.8676384</v>
+      </c>
+      <c r="E127">
+        <v>2024</v>
+      </c>
+      <c r="F127" s="2">
+        <v>71.979259999999996</v>
+      </c>
+      <c r="G127" s="2">
+        <v>4.6941449999999998</v>
+      </c>
+      <c r="H127" s="3">
+        <v>191</v>
+      </c>
+      <c r="I127">
+        <v>25.066666666666666</v>
+      </c>
+    </row>
+    <row r="128" spans="1:9">
+      <c r="A128" t="s">
+        <v>0</v>
+      </c>
+      <c r="B128" t="s">
+        <v>4</v>
+      </c>
+      <c r="C128">
+        <v>69.576505789999999</v>
+      </c>
+      <c r="D128">
+        <v>-138.86729539999999</v>
+      </c>
+      <c r="E128">
+        <v>2024</v>
+      </c>
+      <c r="F128" s="2">
+        <v>72.876679999999993</v>
+      </c>
+      <c r="G128" s="2">
+        <v>2.3661750000000001</v>
+      </c>
+      <c r="H128" s="3">
+        <v>191</v>
+      </c>
+      <c r="I128">
+        <v>19.766666666666666</v>
+      </c>
+    </row>
+    <row r="129" spans="1:9">
+      <c r="A129" t="s">
+        <v>0</v>
+      </c>
+      <c r="B129" t="s">
+        <v>4</v>
+      </c>
+      <c r="C129">
+        <v>69.576544850000005</v>
+      </c>
+      <c r="D129">
+        <v>-138.86699780000001</v>
+      </c>
+      <c r="E129">
+        <v>2024</v>
+      </c>
+      <c r="F129" s="2">
+        <v>73.514600000000002</v>
+      </c>
+      <c r="G129" s="2">
+        <v>4.204345</v>
+      </c>
+      <c r="H129" s="3">
+        <v>191</v>
+      </c>
+      <c r="I129">
+        <v>36.366666666666667</v>
+      </c>
+    </row>
+    <row r="130" spans="1:9">
+      <c r="A130" t="s">
+        <v>0</v>
+      </c>
+      <c r="B130" t="s">
+        <v>5</v>
+      </c>
+      <c r="C130">
+        <v>69.577619990000002</v>
+      </c>
+      <c r="D130">
+        <v>-138.91274999999999</v>
+      </c>
+      <c r="E130">
+        <v>2024</v>
+      </c>
+      <c r="F130" s="2">
+        <v>57.668939999999999</v>
+      </c>
+      <c r="G130" s="2">
+        <v>2.7936839999999998</v>
+      </c>
+      <c r="H130" s="3">
+        <v>191</v>
+      </c>
+      <c r="I130">
+        <v>22.933333333333337</v>
+      </c>
+    </row>
+    <row r="131" spans="1:9">
+      <c r="A131" t="s">
+        <v>0</v>
+      </c>
+      <c r="B131" t="s">
+        <v>5</v>
+      </c>
+      <c r="C131">
+        <v>69.577619990000002</v>
+      </c>
+      <c r="D131">
+        <v>-138.91274999999999</v>
+      </c>
+      <c r="E131">
+        <v>2024</v>
+      </c>
+      <c r="F131" s="2">
+        <v>57.668939999999999</v>
+      </c>
+      <c r="G131" s="2">
+        <v>2.7936839999999998</v>
+      </c>
+      <c r="H131" s="3">
+        <v>191</v>
+      </c>
+      <c r="I131">
+        <v>32.133333333333333</v>
+      </c>
+    </row>
+    <row r="132" spans="1:9">
+      <c r="A132" t="s">
+        <v>0</v>
+      </c>
+      <c r="B132" t="s">
+        <v>5</v>
+      </c>
+      <c r="C132">
+        <v>69.577619990000002</v>
+      </c>
+      <c r="D132">
+        <v>-138.91274999999999</v>
+      </c>
+      <c r="E132">
+        <v>2024</v>
+      </c>
+      <c r="F132" s="2">
+        <v>57.668939999999999</v>
+      </c>
+      <c r="G132" s="2">
+        <v>2.7936839999999998</v>
+      </c>
+      <c r="H132" s="3">
+        <v>191</v>
+      </c>
+      <c r="I132">
+        <v>35.133333333333333</v>
+      </c>
+    </row>
+    <row r="133" spans="1:9">
+      <c r="A133" t="s">
+        <v>0</v>
+      </c>
+      <c r="B133" t="s">
+        <v>5</v>
+      </c>
+      <c r="C133">
+        <v>69.577619990000002</v>
+      </c>
+      <c r="D133">
+        <v>-138.91274999999999</v>
+      </c>
+      <c r="E133">
+        <v>2024</v>
+      </c>
+      <c r="F133" s="2">
+        <v>57.668939999999999</v>
+      </c>
+      <c r="G133" s="2">
+        <v>2.7936839999999998</v>
+      </c>
+      <c r="H133" s="3">
+        <v>191</v>
+      </c>
+      <c r="I133">
+        <v>22.733333333333331</v>
+      </c>
+    </row>
+    <row r="134" spans="1:9">
+      <c r="A134" t="s">
+        <v>0</v>
+      </c>
+      <c r="B134" t="s">
+        <v>5</v>
+      </c>
+      <c r="C134">
+        <v>69.577619990000002</v>
+      </c>
+      <c r="D134">
+        <v>-138.91274999999999</v>
+      </c>
+      <c r="E134">
+        <v>2024</v>
+      </c>
+      <c r="F134" s="2">
+        <v>57.668939999999999</v>
+      </c>
+      <c r="G134" s="2">
+        <v>2.7936839999999998</v>
+      </c>
+      <c r="H134" s="3">
+        <v>191</v>
+      </c>
+      <c r="I134">
+        <v>20.966666666666669</v>
+      </c>
+    </row>
+    <row r="135" spans="1:9">
+      <c r="A135" t="s">
+        <v>0</v>
+      </c>
+      <c r="B135" t="s">
+        <v>6</v>
+      </c>
+      <c r="C135">
+        <v>69.575540020000005</v>
+      </c>
+      <c r="D135">
+        <v>-138.90445</v>
+      </c>
+      <c r="E135">
+        <v>2024</v>
+      </c>
+      <c r="F135" s="2">
+        <v>28.906300000000002</v>
+      </c>
+      <c r="G135" s="2">
+        <v>4.0111990000000004</v>
+      </c>
+      <c r="H135" s="3">
+        <v>191</v>
+      </c>
+      <c r="I135">
+        <v>29.466666666666669</v>
+      </c>
+    </row>
+    <row r="136" spans="1:9">
+      <c r="A136" t="s">
+        <v>0</v>
+      </c>
+      <c r="B136" t="s">
+        <v>6</v>
+      </c>
+      <c r="C136">
+        <v>69.575540020000005</v>
+      </c>
+      <c r="D136">
+        <v>-138.90445</v>
+      </c>
+      <c r="E136">
+        <v>2024</v>
+      </c>
+      <c r="F136" s="2">
+        <v>28.906300000000002</v>
+      </c>
+      <c r="G136" s="2">
+        <v>4.0111990000000004</v>
+      </c>
+      <c r="H136" s="3">
+        <v>191</v>
+      </c>
+      <c r="I136">
+        <v>31.433333333333337</v>
+      </c>
+    </row>
+    <row r="137" spans="1:9">
+      <c r="A137" t="s">
+        <v>0</v>
+      </c>
+      <c r="B137" t="s">
+        <v>6</v>
+      </c>
+      <c r="C137">
+        <v>69.575540020000005</v>
+      </c>
+      <c r="D137">
+        <v>-138.90445</v>
+      </c>
+      <c r="E137">
+        <v>2024</v>
+      </c>
+      <c r="F137" s="2">
+        <v>28.906300000000002</v>
+      </c>
+      <c r="G137" s="2">
+        <v>4.0111990000000004</v>
+      </c>
+      <c r="H137" s="3">
+        <v>191</v>
+      </c>
+      <c r="I137">
+        <v>30.866666666666664</v>
+      </c>
+    </row>
+    <row r="138" spans="1:9">
+      <c r="A138" t="s">
+        <v>0</v>
+      </c>
+      <c r="B138" t="s">
+        <v>6</v>
+      </c>
+      <c r="C138">
+        <v>69.575540020000005</v>
+      </c>
+      <c r="D138">
+        <v>-138.90445</v>
+      </c>
+      <c r="E138">
+        <v>2024</v>
+      </c>
+      <c r="F138" s="2">
+        <v>28.906300000000002</v>
+      </c>
+      <c r="G138" s="2">
+        <v>4.0111990000000004</v>
+      </c>
+      <c r="H138" s="3">
+        <v>191</v>
+      </c>
+      <c r="I138">
+        <v>35.866666666666667</v>
+      </c>
+    </row>
+    <row r="139" spans="1:9">
+      <c r="A139" t="s">
+        <v>0</v>
+      </c>
+      <c r="B139" t="s">
+        <v>6</v>
+      </c>
+      <c r="C139">
+        <v>69.575540020000005</v>
+      </c>
+      <c r="D139">
+        <v>-138.90445</v>
+      </c>
+      <c r="E139">
+        <v>2024</v>
+      </c>
+      <c r="F139" s="2">
+        <v>28.906300000000002</v>
+      </c>
+      <c r="G139" s="2">
+        <v>4.0111990000000004</v>
+      </c>
+      <c r="H139" s="3">
+        <v>191</v>
+      </c>
+      <c r="I139">
+        <v>33.866666666666667</v>
+      </c>
+    </row>
+    <row r="140" spans="1:9">
+      <c r="A140" t="s">
+        <v>0</v>
+      </c>
+      <c r="B140" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C140">
+        <v>69.576106809999999</v>
+      </c>
+      <c r="D140">
+        <v>-138.90396720000001</v>
+      </c>
+      <c r="E140">
+        <v>2024</v>
+      </c>
+      <c r="F140" s="2">
+        <v>32.122779999999999</v>
+      </c>
+      <c r="G140" s="2">
+        <v>6.2787110000000004</v>
+      </c>
+      <c r="H140" s="3">
+        <v>191</v>
+      </c>
+      <c r="I140">
+        <v>38.766666666666666</v>
+      </c>
+    </row>
+    <row r="141" spans="1:9">
+      <c r="A141" t="s">
+        <v>0</v>
+      </c>
+      <c r="B141" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C141">
+        <v>69.576106809999999</v>
+      </c>
+      <c r="D141">
+        <v>-138.90396720000001</v>
+      </c>
+      <c r="E141">
+        <v>2024</v>
+      </c>
+      <c r="F141" s="2">
+        <v>32.122779999999999</v>
+      </c>
+      <c r="G141" s="2">
+        <v>6.2787110000000004</v>
+      </c>
+      <c r="H141" s="3">
+        <v>191</v>
+      </c>
+      <c r="I141">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="142" spans="1:9">
+      <c r="A142" t="s">
+        <v>0</v>
+      </c>
+      <c r="B142" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C142">
+        <v>69.576106809999999</v>
+      </c>
+      <c r="D142">
+        <v>-138.90396720000001</v>
+      </c>
+      <c r="E142">
+        <v>2024</v>
+      </c>
+      <c r="F142" s="2">
+        <v>32.122779999999999</v>
+      </c>
+      <c r="G142" s="2">
+        <v>6.2787110000000004</v>
+      </c>
+      <c r="H142" s="3">
+        <v>191</v>
+      </c>
+      <c r="I142">
+        <v>28.900000000000002</v>
+      </c>
+    </row>
+    <row r="143" spans="1:9">
+      <c r="A143" t="s">
+        <v>0</v>
+      </c>
+      <c r="B143" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C143">
+        <v>69.576106809999999</v>
+      </c>
+      <c r="D143">
+        <v>-138.90396720000001</v>
+      </c>
+      <c r="E143">
+        <v>2024</v>
+      </c>
+      <c r="F143" s="2">
+        <v>32.122779999999999</v>
+      </c>
+      <c r="G143" s="2">
+        <v>6.2787110000000004</v>
+      </c>
+      <c r="H143" s="3">
+        <v>191</v>
+      </c>
+      <c r="I143">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="144" spans="1:9">
+      <c r="A144" t="s">
+        <v>0</v>
+      </c>
+      <c r="B144" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C144">
+        <v>69.576106809999999</v>
+      </c>
+      <c r="D144">
+        <v>-138.90396720000001</v>
+      </c>
+      <c r="E144">
+        <v>2024</v>
+      </c>
+      <c r="F144" s="2">
+        <v>32.122779999999999</v>
+      </c>
+      <c r="G144" s="2">
+        <v>6.2787110000000004</v>
+      </c>
+      <c r="H144" s="3">
+        <v>191</v>
+      </c>
+      <c r="I144">
+        <v>20.366666666666667</v>
+      </c>
+    </row>
+    <row r="145" spans="1:9">
+      <c r="A145" t="s">
+        <v>0</v>
+      </c>
+      <c r="B145" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C145">
+        <v>69.575888039999995</v>
+      </c>
+      <c r="D145">
+        <v>-138.90355299999999</v>
+      </c>
+      <c r="E145">
+        <v>2024</v>
+      </c>
+      <c r="F145" s="2">
+        <v>29.5139</v>
+      </c>
+      <c r="G145" s="2">
+        <v>7.6486470000000004</v>
+      </c>
+      <c r="H145" s="3">
+        <v>191</v>
+      </c>
+      <c r="I145">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="146" spans="1:9">
+      <c r="A146" t="s">
+        <v>0</v>
+      </c>
+      <c r="B146" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C146">
+        <v>69.575888039999995</v>
+      </c>
+      <c r="D146">
+        <v>-138.90355299999999</v>
+      </c>
+      <c r="E146">
+        <v>2024</v>
+      </c>
+      <c r="F146" s="2">
+        <v>29.5139</v>
+      </c>
+      <c r="G146" s="2">
+        <v>7.6486470000000004</v>
+      </c>
+      <c r="H146" s="3">
+        <v>191</v>
+      </c>
+      <c r="I146">
+        <v>40.566666666666663</v>
+      </c>
+    </row>
+    <row r="147" spans="1:9">
+      <c r="A147" t="s">
+        <v>0</v>
+      </c>
+      <c r="B147" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C147">
+        <v>69.575888039999995</v>
+      </c>
+      <c r="D147">
+        <v>-138.90355299999999</v>
+      </c>
+      <c r="E147">
+        <v>2024</v>
+      </c>
+      <c r="F147" s="2">
+        <v>29.5139</v>
+      </c>
+      <c r="G147" s="2">
+        <v>7.6486470000000004</v>
+      </c>
+      <c r="H147" s="3">
+        <v>191</v>
+      </c>
+      <c r="I147">
+        <v>35.1</v>
+      </c>
+    </row>
+    <row r="148" spans="1:9">
+      <c r="A148" t="s">
+        <v>0</v>
+      </c>
+      <c r="B148" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C148">
+        <v>69.575888039999995</v>
+      </c>
+      <c r="D148">
+        <v>-138.90355299999999</v>
+      </c>
+      <c r="E148">
+        <v>2024</v>
+      </c>
+      <c r="F148" s="2">
+        <v>29.5139</v>
+      </c>
+      <c r="G148" s="2">
+        <v>7.6486470000000004</v>
+      </c>
+      <c r="H148" s="3">
+        <v>191</v>
+      </c>
+      <c r="I148">
+        <v>37.233333333333327</v>
+      </c>
+    </row>
+    <row r="149" spans="1:9">
+      <c r="A149" t="s">
+        <v>0</v>
+      </c>
+      <c r="B149" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C149">
+        <v>69.575888039999995</v>
+      </c>
+      <c r="D149">
+        <v>-138.90355299999999</v>
+      </c>
+      <c r="E149">
+        <v>2024</v>
+      </c>
+      <c r="F149" s="2">
+        <v>29.5139</v>
+      </c>
+      <c r="G149" s="2">
+        <v>7.6486470000000004</v>
+      </c>
+      <c r="H149" s="3">
+        <v>191</v>
+      </c>
+      <c r="I149">
+        <v>34.9</v>
+      </c>
+    </row>
+    <row r="150" spans="1:9">
+      <c r="A150" t="s">
+        <v>0</v>
+      </c>
+      <c r="B150" t="s">
+        <v>3</v>
+      </c>
+      <c r="C150">
+        <v>69.574881039999994</v>
+      </c>
+      <c r="D150">
+        <v>-138.86307059999999</v>
+      </c>
+      <c r="E150">
+        <v>2024</v>
+      </c>
+      <c r="F150" s="2">
+        <v>71.664990000000003</v>
+      </c>
+      <c r="G150" s="2">
+        <v>1.0686739999999999</v>
+      </c>
+      <c r="H150" s="3">
+        <v>202</v>
+      </c>
+      <c r="I150">
+        <v>51.666666666666664</v>
+      </c>
+    </row>
+    <row r="151" spans="1:9">
+      <c r="A151" t="s">
+        <v>0</v>
+      </c>
+      <c r="B151" t="s">
+        <v>3</v>
+      </c>
+      <c r="C151">
+        <v>69.574888920000006</v>
+      </c>
+      <c r="D151">
+        <v>-138.8631728</v>
+      </c>
+      <c r="E151">
+        <v>2024</v>
+      </c>
+      <c r="F151" s="2">
+        <v>71.566590000000005</v>
+      </c>
+      <c r="G151" s="2">
+        <v>3.236253</v>
+      </c>
+      <c r="H151" s="3">
+        <v>202</v>
+      </c>
+      <c r="I151">
+        <v>46.833333333333336</v>
+      </c>
+    </row>
+    <row r="152" spans="1:9">
+      <c r="A152" t="s">
+        <v>0</v>
+      </c>
+      <c r="B152" t="s">
+        <v>3</v>
+      </c>
+      <c r="C152">
+        <v>69.574882380000005</v>
+      </c>
+      <c r="D152">
+        <v>-138.8634658</v>
+      </c>
+      <c r="E152">
+        <v>2024</v>
+      </c>
+      <c r="F152" s="2">
+        <v>71.334130000000002</v>
+      </c>
+      <c r="G152" s="2">
+        <v>2.6920440000000001</v>
+      </c>
+      <c r="H152" s="3">
+        <v>202</v>
+      </c>
+      <c r="I152">
+        <v>45.166666666666664</v>
+      </c>
+    </row>
+    <row r="153" spans="1:9">
+      <c r="A153" t="s">
+        <v>0</v>
+      </c>
+      <c r="B153" t="s">
+        <v>3</v>
+      </c>
+      <c r="C153">
+        <v>69.574860330000007</v>
+      </c>
+      <c r="D153">
+        <v>-138.8637913</v>
+      </c>
+      <c r="E153">
+        <v>2024</v>
+      </c>
+      <c r="F153" s="2">
+        <v>71.194389999999999</v>
+      </c>
+      <c r="G153" s="2">
+        <v>1.1705080000000001</v>
+      </c>
+      <c r="H153" s="3">
+        <v>202</v>
+      </c>
+      <c r="I153">
+        <v>38.166666666666664</v>
+      </c>
+    </row>
+    <row r="154" spans="1:9">
+      <c r="A154" t="s">
+        <v>0</v>
+      </c>
+      <c r="B154" t="s">
+        <v>3</v>
+      </c>
+      <c r="C154">
+        <v>69.574861170000005</v>
+      </c>
+      <c r="D154">
+        <v>-138.86387010000001</v>
+      </c>
+      <c r="E154">
+        <v>2024</v>
+      </c>
+      <c r="F154" s="2">
+        <v>71.170460000000006</v>
+      </c>
+      <c r="G154" s="2">
+        <v>1.1862360000000001</v>
+      </c>
+      <c r="H154" s="3">
+        <v>202</v>
+      </c>
+      <c r="I154">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="155" spans="1:9">
+      <c r="A155" t="s">
+        <v>0</v>
+      </c>
+      <c r="B155" t="s">
+        <v>3</v>
+      </c>
+      <c r="C155">
+        <v>69.574857399999999</v>
+      </c>
+      <c r="D155">
+        <v>-138.8640747</v>
+      </c>
+      <c r="E155">
+        <v>2024</v>
+      </c>
+      <c r="F155" s="2">
+        <v>71.030659999999997</v>
+      </c>
+      <c r="G155" s="2">
+        <v>1.785264</v>
+      </c>
+      <c r="H155" s="3">
+        <v>202</v>
+      </c>
+      <c r="I155">
+        <v>36.666666666666664</v>
+      </c>
+    </row>
+    <row r="156" spans="1:9">
+      <c r="A156" t="s">
+        <v>0</v>
+      </c>
+      <c r="B156" t="s">
+        <v>4</v>
+      </c>
+      <c r="C156">
+        <v>69.576416179999995</v>
+      </c>
+      <c r="D156">
+        <v>-138.86817970000001</v>
+      </c>
+      <c r="E156">
+        <v>2024</v>
+      </c>
+      <c r="F156" s="2">
+        <v>71.11157</v>
+      </c>
+      <c r="G156" s="2">
+        <v>3.3767399999999999</v>
+      </c>
+      <c r="H156" s="3">
+        <v>202</v>
+      </c>
+      <c r="I156">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="157" spans="1:9">
+      <c r="A157" t="s">
+        <v>0</v>
+      </c>
+      <c r="B157" t="s">
+        <v>4</v>
+      </c>
+      <c r="C157">
+        <v>69.576403529999993</v>
+      </c>
+      <c r="D157">
+        <v>-138.86811879999999</v>
+      </c>
+      <c r="E157">
+        <v>2024</v>
+      </c>
+      <c r="F157" s="2">
+        <v>71.146529999999998</v>
+      </c>
+      <c r="G157" s="2">
+        <v>2.5742989999999999</v>
+      </c>
+      <c r="H157" s="3">
+        <v>202</v>
+      </c>
+      <c r="I157">
+        <v>26.333333333333332</v>
+      </c>
+    </row>
+    <row r="158" spans="1:9">
+      <c r="A158" t="s">
+        <v>0</v>
+      </c>
+      <c r="B158" t="s">
+        <v>4</v>
+      </c>
+      <c r="C158">
+        <v>69.576461190000003</v>
+      </c>
+      <c r="D158">
+        <v>-138.86773909999999</v>
+      </c>
+      <c r="E158">
+        <v>2024</v>
+      </c>
+      <c r="F158" s="2">
+        <v>71.806269999999998</v>
+      </c>
+      <c r="G158" s="2">
+        <v>4.376296</v>
+      </c>
+      <c r="H158" s="3">
+        <v>202</v>
+      </c>
+      <c r="I158">
+        <v>21.666666666666668</v>
+      </c>
+    </row>
+    <row r="159" spans="1:9">
+      <c r="A159" t="s">
+        <v>0</v>
+      </c>
+      <c r="B159" t="s">
+        <v>4</v>
+      </c>
+      <c r="C159">
+        <v>69.576468489999996</v>
+      </c>
+      <c r="D159">
+        <v>-138.8676384</v>
+      </c>
+      <c r="E159">
+        <v>2024</v>
+      </c>
+      <c r="F159" s="2">
+        <v>71.979259999999996</v>
+      </c>
+      <c r="G159" s="2">
+        <v>4.6941449999999998</v>
+      </c>
+      <c r="H159" s="3">
+        <v>202</v>
+      </c>
+      <c r="I159">
+        <v>18.5</v>
+      </c>
+    </row>
+    <row r="160" spans="1:9">
+      <c r="A160" t="s">
+        <v>0</v>
+      </c>
+      <c r="B160" t="s">
+        <v>4</v>
+      </c>
+      <c r="C160">
+        <v>69.576505789999999</v>
+      </c>
+      <c r="D160">
+        <v>-138.86729539999999</v>
+      </c>
+      <c r="E160">
+        <v>2024</v>
+      </c>
+      <c r="F160" s="2">
+        <v>72.876679999999993</v>
+      </c>
+      <c r="G160" s="2">
+        <v>2.3661750000000001</v>
+      </c>
+      <c r="H160" s="3">
+        <v>202</v>
+      </c>
+      <c r="I160">
+        <v>20.833333333333332</v>
+      </c>
+    </row>
+    <row r="161" spans="1:9">
+      <c r="A161" t="s">
+        <v>0</v>
+      </c>
+      <c r="B161" t="s">
+        <v>4</v>
+      </c>
+      <c r="C161">
+        <v>69.576544850000005</v>
+      </c>
+      <c r="D161">
+        <v>-138.86699780000001</v>
+      </c>
+      <c r="E161">
+        <v>2024</v>
+      </c>
+      <c r="F161" s="2">
+        <v>73.514600000000002</v>
+      </c>
+      <c r="G161" s="2">
+        <v>4.204345</v>
+      </c>
+      <c r="H161" s="3">
+        <v>202</v>
+      </c>
+      <c r="I161">
+        <v>27.666666666666668</v>
+      </c>
+    </row>
+    <row r="162" spans="1:9">
+      <c r="A162" t="s">
+        <v>0</v>
+      </c>
+      <c r="B162" t="s">
+        <v>5</v>
+      </c>
+      <c r="C162">
+        <v>69.577619990000002</v>
+      </c>
+      <c r="D162">
+        <v>-138.91274999999999</v>
+      </c>
+      <c r="E162">
+        <v>2024</v>
+      </c>
+      <c r="F162" s="2">
+        <v>57.668939999999999</v>
+      </c>
+      <c r="G162" s="2">
+        <v>2.7936839999999998</v>
+      </c>
+      <c r="H162" s="3">
+        <v>211</v>
+      </c>
+      <c r="I162">
+        <v>32.6</v>
+      </c>
+    </row>
+    <row r="163" spans="1:9">
+      <c r="A163" t="s">
+        <v>0</v>
+      </c>
+      <c r="B163" t="s">
+        <v>5</v>
+      </c>
+      <c r="C163">
+        <v>69.577619990000002</v>
+      </c>
+      <c r="D163">
+        <v>-138.91274999999999</v>
+      </c>
+      <c r="E163">
+        <v>2024</v>
+      </c>
+      <c r="F163" s="2">
+        <v>57.668939999999999</v>
+      </c>
+      <c r="G163" s="2">
+        <v>2.7936839999999998</v>
+      </c>
+      <c r="H163" s="3">
+        <v>211</v>
+      </c>
+      <c r="I163">
+        <v>41.466666666666669</v>
+      </c>
+    </row>
+    <row r="164" spans="1:9">
+      <c r="A164" t="s">
+        <v>0</v>
+      </c>
+      <c r="B164" t="s">
+        <v>5</v>
+      </c>
+      <c r="C164">
+        <v>69.577619990000002</v>
+      </c>
+      <c r="D164">
+        <v>-138.91274999999999</v>
+      </c>
+      <c r="E164">
+        <v>2024</v>
+      </c>
+      <c r="F164" s="2">
+        <v>57.668939999999999</v>
+      </c>
+      <c r="G164" s="2">
+        <v>2.7936839999999998</v>
+      </c>
+      <c r="H164" s="3">
+        <v>211</v>
+      </c>
+      <c r="I164">
+        <v>38.866666666666667</v>
+      </c>
+    </row>
+    <row r="165" spans="1:9">
+      <c r="A165" t="s">
+        <v>0</v>
+      </c>
+      <c r="B165" t="s">
+        <v>5</v>
+      </c>
+      <c r="C165">
+        <v>69.577619990000002</v>
+      </c>
+      <c r="D165">
+        <v>-138.91274999999999</v>
+      </c>
+      <c r="E165">
+        <v>2024</v>
+      </c>
+      <c r="F165" s="2">
+        <v>57.668939999999999</v>
+      </c>
+      <c r="G165" s="2">
+        <v>2.7936839999999998</v>
+      </c>
+      <c r="H165" s="3">
+        <v>211</v>
+      </c>
+      <c r="I165">
+        <v>38.666666666666664</v>
+      </c>
+    </row>
+    <row r="166" spans="1:9">
+      <c r="A166" t="s">
+        <v>0</v>
+      </c>
+      <c r="B166" t="s">
+        <v>5</v>
+      </c>
+      <c r="C166">
+        <v>69.577619990000002</v>
+      </c>
+      <c r="D166">
+        <v>-138.91274999999999</v>
+      </c>
+      <c r="E166">
+        <v>2024</v>
+      </c>
+      <c r="F166" s="2">
+        <v>57.668939999999999</v>
+      </c>
+      <c r="G166" s="2">
+        <v>2.7936839999999998</v>
+      </c>
+      <c r="H166" s="3">
+        <v>211</v>
+      </c>
+      <c r="I166">
+        <v>33.300000000000004</v>
+      </c>
+    </row>
+    <row r="167" spans="1:9">
+      <c r="A167" t="s">
+        <v>0</v>
+      </c>
+      <c r="B167" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C167">
+        <v>69.576106809999999</v>
+      </c>
+      <c r="D167">
+        <v>-138.90396720000001</v>
+      </c>
+      <c r="E167">
+        <v>2024</v>
+      </c>
+      <c r="F167" s="2">
+        <v>32.122779999999999</v>
+      </c>
+      <c r="G167" s="2">
+        <v>6.2787110000000004</v>
+      </c>
+      <c r="H167" s="3">
+        <v>211</v>
+      </c>
+      <c r="I167">
+        <v>62.366666666666667</v>
+      </c>
+    </row>
+    <row r="168" spans="1:9">
+      <c r="A168" t="s">
+        <v>0</v>
+      </c>
+      <c r="B168" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C168">
+        <v>69.576106809999999</v>
+      </c>
+      <c r="D168">
+        <v>-138.90396720000001</v>
+      </c>
+      <c r="E168">
+        <v>2024</v>
+      </c>
+      <c r="F168" s="2">
+        <v>32.122779999999999</v>
+      </c>
+      <c r="G168" s="2">
+        <v>6.2787110000000004</v>
+      </c>
+      <c r="H168" s="3">
+        <v>211</v>
+      </c>
+      <c r="I168">
+        <v>59.066666666666663</v>
+      </c>
+    </row>
+    <row r="169" spans="1:9">
+      <c r="A169" t="s">
+        <v>0</v>
+      </c>
+      <c r="B169" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C169">
+        <v>69.576106809999999</v>
+      </c>
+      <c r="D169">
+        <v>-138.90396720000001</v>
+      </c>
+      <c r="E169">
+        <v>2024</v>
+      </c>
+      <c r="F169" s="2">
+        <v>32.122779999999999</v>
+      </c>
+      <c r="G169" s="2">
+        <v>6.2787110000000004</v>
+      </c>
+      <c r="H169" s="3">
+        <v>211</v>
+      </c>
+      <c r="I169">
+        <v>50.166666666666664</v>
+      </c>
+    </row>
+    <row r="170" spans="1:9">
+      <c r="A170" t="s">
+        <v>0</v>
+      </c>
+      <c r="B170" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C170">
+        <v>69.576106809999999</v>
+      </c>
+      <c r="D170">
+        <v>-138.90396720000001</v>
+      </c>
+      <c r="E170">
+        <v>2024</v>
+      </c>
+      <c r="F170" s="2">
+        <v>32.122779999999999</v>
+      </c>
+      <c r="G170" s="2">
+        <v>6.2787110000000004</v>
+      </c>
+      <c r="H170" s="3">
+        <v>211</v>
+      </c>
+      <c r="I170">
+        <v>42.9</v>
+      </c>
+    </row>
+    <row r="171" spans="1:9">
+      <c r="A171" t="s">
+        <v>0</v>
+      </c>
+      <c r="B171" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C171">
+        <v>69.576106809999999</v>
+      </c>
+      <c r="D171">
+        <v>-138.90396720000001</v>
+      </c>
+      <c r="E171">
+        <v>2024</v>
+      </c>
+      <c r="F171" s="2">
+        <v>32.122779999999999</v>
+      </c>
+      <c r="G171" s="2">
+        <v>6.2787110000000004</v>
+      </c>
+      <c r="H171" s="3">
+        <v>211</v>
+      </c>
+      <c r="I171">
+        <v>41.466666666666661</v>
+      </c>
+    </row>
+    <row r="172" spans="1:9">
+      <c r="A172" t="s">
+        <v>0</v>
+      </c>
+      <c r="B172" t="s">
+        <v>6</v>
+      </c>
+      <c r="C172">
+        <v>69.575540020000005</v>
+      </c>
+      <c r="D172">
+        <v>-138.90445</v>
+      </c>
+      <c r="E172">
+        <v>2024</v>
+      </c>
+      <c r="F172" s="2">
+        <v>28.906300000000002</v>
+      </c>
+      <c r="G172" s="2">
+        <v>4.0111990000000004</v>
+      </c>
+      <c r="H172" s="3">
+        <v>211</v>
+      </c>
+      <c r="I172">
+        <v>28.166666666666668</v>
+      </c>
+    </row>
+    <row r="173" spans="1:9">
+      <c r="A173" t="s">
+        <v>0</v>
+      </c>
+      <c r="B173" t="s">
+        <v>6</v>
+      </c>
+      <c r="C173">
+        <v>69.575540020000005</v>
+      </c>
+      <c r="D173">
+        <v>-138.90445</v>
+      </c>
+      <c r="E173">
+        <v>2024</v>
+      </c>
+      <c r="F173" s="2">
+        <v>28.906300000000002</v>
+      </c>
+      <c r="G173" s="2">
+        <v>4.0111990000000004</v>
+      </c>
+      <c r="H173" s="3">
+        <v>211</v>
+      </c>
+      <c r="I173">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="174" spans="1:9">
+      <c r="A174" t="s">
+        <v>0</v>
+      </c>
+      <c r="B174" t="s">
+        <v>6</v>
+      </c>
+      <c r="C174">
+        <v>69.575540020000005</v>
+      </c>
+      <c r="D174">
+        <v>-138.90445</v>
+      </c>
+      <c r="E174">
+        <v>2024</v>
+      </c>
+      <c r="F174" s="2">
+        <v>28.906300000000002</v>
+      </c>
+      <c r="G174" s="2">
+        <v>4.0111990000000004</v>
+      </c>
+      <c r="H174" s="3">
+        <v>211</v>
+      </c>
+      <c r="I174">
+        <v>46.833333333333336</v>
+      </c>
+    </row>
+    <row r="175" spans="1:9">
+      <c r="A175" t="s">
+        <v>0</v>
+      </c>
+      <c r="B175" t="s">
+        <v>6</v>
+      </c>
+      <c r="C175">
+        <v>69.575540020000005</v>
+      </c>
+      <c r="D175">
+        <v>-138.90445</v>
+      </c>
+      <c r="E175">
+        <v>2024</v>
+      </c>
+      <c r="F175" s="2">
+        <v>28.906300000000002</v>
+      </c>
+      <c r="G175" s="2">
+        <v>4.0111990000000004</v>
+      </c>
+      <c r="H175" s="3">
+        <v>211</v>
+      </c>
+      <c r="I175">
+        <v>50.066666666666663</v>
+      </c>
+    </row>
+    <row r="176" spans="1:9">
+      <c r="A176" t="s">
+        <v>0</v>
+      </c>
+      <c r="B176" t="s">
+        <v>6</v>
+      </c>
+      <c r="C176">
+        <v>69.575540020000005</v>
+      </c>
+      <c r="D176">
+        <v>-138.90445</v>
+      </c>
+      <c r="E176">
+        <v>2024</v>
+      </c>
+      <c r="F176" s="2">
+        <v>28.906300000000002</v>
+      </c>
+      <c r="G176" s="2">
+        <v>4.0111990000000004</v>
+      </c>
+      <c r="H176" s="3">
+        <v>211</v>
+      </c>
+      <c r="I176">
+        <v>52.733333333333327</v>
+      </c>
+    </row>
+    <row r="177" spans="1:9">
+      <c r="A177" t="s">
+        <v>0</v>
+      </c>
+      <c r="B177" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C177">
+        <v>69.575888039999995</v>
+      </c>
+      <c r="D177">
+        <v>-138.90355299999999</v>
+      </c>
+      <c r="E177">
+        <v>2024</v>
+      </c>
+      <c r="F177" s="2">
+        <v>29.5139</v>
+      </c>
+      <c r="G177" s="2">
+        <v>7.6486470000000004</v>
+      </c>
+      <c r="H177" s="3">
+        <v>211</v>
+      </c>
+      <c r="I177">
+        <v>60.699999999999996</v>
+      </c>
+    </row>
+    <row r="178" spans="1:9">
+      <c r="A178" t="s">
+        <v>0</v>
+      </c>
+      <c r="B178" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C178">
+        <v>69.575888039999995</v>
+      </c>
+      <c r="D178">
+        <v>-138.90355299999999</v>
+      </c>
+      <c r="E178">
+        <v>2024</v>
+      </c>
+      <c r="F178" s="2">
+        <v>29.5139</v>
+      </c>
+      <c r="G178" s="2">
+        <v>7.6486470000000004</v>
+      </c>
+      <c r="H178" s="3">
+        <v>211</v>
+      </c>
+      <c r="I178">
+        <v>54.300000000000004</v>
+      </c>
+    </row>
+    <row r="179" spans="1:9">
+      <c r="A179" t="s">
+        <v>0</v>
+      </c>
+      <c r="B179" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C179">
+        <v>69.575888039999995</v>
+      </c>
+      <c r="D179">
+        <v>-138.90355299999999</v>
+      </c>
+      <c r="E179">
+        <v>2024</v>
+      </c>
+      <c r="F179" s="2">
+        <v>29.5139</v>
+      </c>
+      <c r="G179" s="2">
+        <v>7.6486470000000004</v>
+      </c>
+      <c r="H179" s="3">
+        <v>211</v>
+      </c>
+      <c r="I179">
+        <v>56.566666666666663</v>
+      </c>
+    </row>
+    <row r="180" spans="1:9">
+      <c r="A180" t="s">
+        <v>0</v>
+      </c>
+      <c r="B180" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C180">
+        <v>69.575888039999995</v>
+      </c>
+      <c r="D180">
+        <v>-138.90355299999999</v>
+      </c>
+      <c r="E180">
+        <v>2024</v>
+      </c>
+      <c r="F180" s="2">
+        <v>29.5139</v>
+      </c>
+      <c r="G180" s="2">
+        <v>7.6486470000000004</v>
+      </c>
+      <c r="H180" s="3">
+        <v>211</v>
+      </c>
+      <c r="I180">
+        <v>53.1</v>
+      </c>
+    </row>
+    <row r="181" spans="1:9">
+      <c r="A181" t="s">
+        <v>0</v>
+      </c>
+      <c r="B181" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C181">
+        <v>69.575888039999995</v>
+      </c>
+      <c r="D181">
+        <v>-138.90355299999999</v>
+      </c>
+      <c r="E181">
+        <v>2024</v>
+      </c>
+      <c r="F181" s="2">
+        <v>29.5139</v>
+      </c>
+      <c r="G181" s="2">
+        <v>7.6486470000000004</v>
+      </c>
+      <c r="H181" s="3">
+        <v>211</v>
+      </c>
+      <c r="I181">
+        <v>61.4</v>
+      </c>
+    </row>
+    <row r="182" spans="1:9">
+      <c r="A182" t="s">
+        <v>0</v>
+      </c>
+      <c r="B182" t="s">
+        <v>3</v>
+      </c>
+      <c r="C182">
+        <v>69.574881039999994</v>
+      </c>
+      <c r="D182">
+        <v>-138.86307059999999</v>
+      </c>
+      <c r="E182">
+        <v>2024</v>
+      </c>
+      <c r="F182" s="2">
+        <v>71.664990000000003</v>
+      </c>
+      <c r="G182" s="2">
+        <v>1.0686739999999999</v>
+      </c>
+      <c r="H182" s="3">
+        <v>213</v>
+      </c>
+      <c r="I182">
+        <v>57.733333333333327</v>
+      </c>
+    </row>
+    <row r="183" spans="1:9">
+      <c r="A183" t="s">
+        <v>0</v>
+      </c>
+      <c r="B183" t="s">
+        <v>3</v>
+      </c>
+      <c r="C183">
+        <v>69.574888920000006</v>
+      </c>
+      <c r="D183">
+        <v>-138.8631728</v>
+      </c>
+      <c r="E183">
+        <v>2024</v>
+      </c>
+      <c r="F183" s="2">
+        <v>71.566590000000005</v>
+      </c>
+      <c r="G183" s="2">
+        <v>3.236253</v>
+      </c>
+      <c r="H183" s="3">
+        <v>213</v>
+      </c>
+      <c r="I183">
+        <v>57.266666666666673</v>
+      </c>
+    </row>
+    <row r="184" spans="1:9">
+      <c r="A184" t="s">
+        <v>0</v>
+      </c>
+      <c r="B184" t="s">
+        <v>3</v>
+      </c>
+      <c r="C184">
+        <v>69.574882380000005</v>
+      </c>
+      <c r="D184">
+        <v>-138.8634658</v>
+      </c>
+      <c r="E184">
+        <v>2024</v>
+      </c>
+      <c r="F184" s="2">
+        <v>71.334130000000002</v>
+      </c>
+      <c r="G184" s="2">
+        <v>2.6920440000000001</v>
+      </c>
+      <c r="H184" s="3">
+        <v>213</v>
+      </c>
+      <c r="I184">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="185" spans="1:9">
+      <c r="A185" t="s">
+        <v>0</v>
+      </c>
+      <c r="B185" t="s">
+        <v>3</v>
+      </c>
+      <c r="C185">
+        <v>69.574860330000007</v>
+      </c>
+      <c r="D185">
+        <v>-138.8637913</v>
+      </c>
+      <c r="E185">
+        <v>2024</v>
+      </c>
+      <c r="F185" s="2">
+        <v>71.194389999999999</v>
+      </c>
+      <c r="G185" s="2">
+        <v>1.1705080000000001</v>
+      </c>
+      <c r="H185" s="3">
+        <v>213</v>
+      </c>
+      <c r="I185">
+        <v>62.266666666666673</v>
+      </c>
+    </row>
+    <row r="186" spans="1:9">
+      <c r="A186" t="s">
+        <v>0</v>
+      </c>
+      <c r="B186" t="s">
+        <v>3</v>
+      </c>
+      <c r="C186">
+        <v>69.574861170000005</v>
+      </c>
+      <c r="D186">
+        <v>-138.86387010000001</v>
+      </c>
+      <c r="E186">
+        <v>2024</v>
+      </c>
+      <c r="F186" s="2">
+        <v>71.170460000000006</v>
+      </c>
+      <c r="G186" s="2">
+        <v>1.1862360000000001</v>
+      </c>
+      <c r="H186" s="3">
+        <v>213</v>
+      </c>
+      <c r="I186">
+        <v>62.333333333333336</v>
+      </c>
+    </row>
+    <row r="187" spans="1:9">
+      <c r="A187" t="s">
+        <v>0</v>
+      </c>
+      <c r="B187" t="s">
+        <v>3</v>
+      </c>
+      <c r="C187">
+        <v>69.574857399999999</v>
+      </c>
+      <c r="D187">
+        <v>-138.8640747</v>
+      </c>
+      <c r="E187">
+        <v>2024</v>
+      </c>
+      <c r="F187" s="2">
+        <v>71.030659999999997</v>
+      </c>
+      <c r="G187" s="2">
+        <v>1.785264</v>
+      </c>
+      <c r="H187" s="3">
+        <v>213</v>
+      </c>
+      <c r="I187">
+        <v>63.033333333333339</v>
+      </c>
+    </row>
+    <row r="188" spans="1:9">
+      <c r="A188" t="s">
+        <v>0</v>
+      </c>
+      <c r="B188" t="s">
+        <v>4</v>
+      </c>
+      <c r="C188">
+        <v>69.576416179999995</v>
+      </c>
+      <c r="D188">
+        <v>-138.86817970000001</v>
+      </c>
+      <c r="E188">
+        <v>2024</v>
+      </c>
+      <c r="F188" s="2">
+        <v>71.11157</v>
+      </c>
+      <c r="G188" s="2">
+        <v>3.3767399999999999</v>
+      </c>
+      <c r="H188" s="3">
+        <v>213</v>
+      </c>
+      <c r="I188">
+        <v>47.066666666666663</v>
+      </c>
+    </row>
+    <row r="189" spans="1:9">
+      <c r="A189" t="s">
+        <v>0</v>
+      </c>
+      <c r="B189" t="s">
+        <v>4</v>
+      </c>
+      <c r="C189">
+        <v>69.576403529999993</v>
+      </c>
+      <c r="D189">
+        <v>-138.86811879999999</v>
+      </c>
+      <c r="E189">
+        <v>2024</v>
+      </c>
+      <c r="F189" s="2">
+        <v>71.146529999999998</v>
+      </c>
+      <c r="G189" s="2">
+        <v>2.5742989999999999</v>
+      </c>
+      <c r="H189" s="3">
+        <v>213</v>
+      </c>
+      <c r="I189">
+        <v>44.466666666666669</v>
+      </c>
+    </row>
+    <row r="190" spans="1:9">
+      <c r="A190" t="s">
+        <v>0</v>
+      </c>
+      <c r="B190" t="s">
+        <v>4</v>
+      </c>
+      <c r="C190">
+        <v>69.576461190000003</v>
+      </c>
+      <c r="D190">
+        <v>-138.86773909999999</v>
+      </c>
+      <c r="E190">
+        <v>2024</v>
+      </c>
+      <c r="F190" s="2">
+        <v>71.806269999999998</v>
+      </c>
+      <c r="G190" s="2">
+        <v>4.376296</v>
+      </c>
+      <c r="H190" s="3">
+        <v>213</v>
+      </c>
+      <c r="I190">
+        <v>36.6</v>
+      </c>
+    </row>
+    <row r="191" spans="1:9">
+      <c r="A191" t="s">
+        <v>0</v>
+      </c>
+      <c r="B191" t="s">
+        <v>4</v>
+      </c>
+      <c r="C191">
+        <v>69.576468489999996</v>
+      </c>
+      <c r="D191">
+        <v>-138.8676384</v>
+      </c>
+      <c r="E191">
+        <v>2024</v>
+      </c>
+      <c r="F191" s="2">
+        <v>71.979259999999996</v>
+      </c>
+      <c r="G191" s="2">
+        <v>4.6941449999999998</v>
+      </c>
+      <c r="H191" s="3">
+        <v>213</v>
+      </c>
+      <c r="I191">
+        <v>37.133333333333333</v>
+      </c>
+    </row>
+    <row r="192" spans="1:9">
+      <c r="A192" t="s">
+        <v>0</v>
+      </c>
+      <c r="B192" t="s">
+        <v>4</v>
+      </c>
+      <c r="C192">
+        <v>69.576505789999999</v>
+      </c>
+      <c r="D192">
+        <v>-138.86729539999999</v>
+      </c>
+      <c r="E192">
+        <v>2024</v>
+      </c>
+      <c r="F192" s="2">
+        <v>72.876679999999993</v>
+      </c>
+      <c r="G192" s="2">
+        <v>2.3661750000000001</v>
+      </c>
+      <c r="H192" s="3">
+        <v>213</v>
+      </c>
+      <c r="I192">
+        <v>37.033333333333331</v>
+      </c>
+    </row>
+    <row r="193" spans="1:9">
+      <c r="A193" t="s">
+        <v>0</v>
+      </c>
+      <c r="B193" t="s">
+        <v>4</v>
+      </c>
+      <c r="C193">
+        <v>69.576544850000005</v>
+      </c>
+      <c r="D193">
+        <v>-138.86699780000001</v>
+      </c>
+      <c r="E193">
+        <v>2024</v>
+      </c>
+      <c r="F193" s="2">
+        <v>73.514600000000002</v>
+      </c>
+      <c r="G193" s="2">
+        <v>4.204345</v>
+      </c>
+      <c r="H193" s="3">
+        <v>213</v>
+      </c>
+      <c r="I193">
+        <v>50.9</v>
+      </c>
+    </row>
+    <row r="194" spans="1:9">
+      <c r="A194" t="s">
+        <v>0</v>
+      </c>
+      <c r="B194" t="s">
+        <v>5</v>
+      </c>
+      <c r="C194">
+        <v>69.577619990000002</v>
+      </c>
+      <c r="D194">
+        <v>-138.91274999999999</v>
+      </c>
+      <c r="E194">
+        <v>2024</v>
+      </c>
+      <c r="F194" s="2">
+        <v>57.668939999999999</v>
+      </c>
+      <c r="G194" s="2">
+        <v>2.7936839999999998</v>
+      </c>
+      <c r="H194" s="3">
+        <v>223</v>
+      </c>
+      <c r="I194">
+        <v>40.733333333333327</v>
+      </c>
+    </row>
+    <row r="195" spans="1:9">
+      <c r="A195" t="s">
+        <v>0</v>
+      </c>
+      <c r="B195" t="s">
+        <v>5</v>
+      </c>
+      <c r="C195">
+        <v>69.577619990000002</v>
+      </c>
+      <c r="D195">
+        <v>-138.91274999999999</v>
+      </c>
+      <c r="E195">
+        <v>2024</v>
+      </c>
+      <c r="F195" s="2">
+        <v>57.668939999999999</v>
+      </c>
+      <c r="G195" s="2">
+        <v>2.7936839999999998</v>
+      </c>
+      <c r="H195" s="3">
+        <v>223</v>
+      </c>
+      <c r="I195">
+        <v>46.5</v>
+      </c>
+    </row>
+    <row r="196" spans="1:9">
+      <c r="A196" t="s">
+        <v>0</v>
+      </c>
+      <c r="B196" t="s">
+        <v>5</v>
+      </c>
+      <c r="C196">
+        <v>69.577619990000002</v>
+      </c>
+      <c r="D196">
+        <v>-138.91274999999999</v>
+      </c>
+      <c r="E196">
+        <v>2024</v>
+      </c>
+      <c r="F196" s="2">
+        <v>57.668939999999999</v>
+      </c>
+      <c r="G196" s="2">
+        <v>2.7936839999999998</v>
+      </c>
+      <c r="H196" s="3">
+        <v>223</v>
+      </c>
+      <c r="I196">
+        <v>44.933333333333337</v>
+      </c>
+    </row>
+    <row r="197" spans="1:9">
+      <c r="A197" t="s">
+        <v>0</v>
+      </c>
+      <c r="B197" t="s">
+        <v>5</v>
+      </c>
+      <c r="C197">
+        <v>69.577619990000002</v>
+      </c>
+      <c r="D197">
+        <v>-138.91274999999999</v>
+      </c>
+      <c r="E197">
+        <v>2024</v>
+      </c>
+      <c r="F197" s="2">
+        <v>57.668939999999999</v>
+      </c>
+      <c r="G197" s="2">
+        <v>2.7936839999999998</v>
+      </c>
+      <c r="H197" s="3">
+        <v>223</v>
+      </c>
+      <c r="I197">
+        <v>40.299999999999997</v>
+      </c>
+    </row>
+    <row r="198" spans="1:9">
+      <c r="A198" t="s">
+        <v>0</v>
+      </c>
+      <c r="B198" t="s">
+        <v>5</v>
+      </c>
+      <c r="C198">
+        <v>69.577619990000002</v>
+      </c>
+      <c r="D198">
+        <v>-138.91274999999999</v>
+      </c>
+      <c r="E198">
+        <v>2024</v>
+      </c>
+      <c r="F198" s="2">
+        <v>57.668939999999999</v>
+      </c>
+      <c r="G198" s="2">
+        <v>2.7936839999999998</v>
+      </c>
+      <c r="H198" s="3">
+        <v>223</v>
+      </c>
+      <c r="I198">
+        <v>34.433333333333337</v>
+      </c>
+    </row>
+    <row r="199" spans="1:9">
+      <c r="A199" t="s">
+        <v>0</v>
+      </c>
+      <c r="B199" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C199">
+        <v>69.576106809999999</v>
+      </c>
+      <c r="D199">
+        <v>-138.90396720000001</v>
+      </c>
+      <c r="E199">
+        <v>2024</v>
+      </c>
+      <c r="F199" s="2">
+        <v>32.122779999999999</v>
+      </c>
+      <c r="G199" s="2">
+        <v>6.2787110000000004</v>
+      </c>
+      <c r="H199" s="3">
+        <v>223</v>
+      </c>
+      <c r="I199">
+        <v>69.466666666666669</v>
+      </c>
+    </row>
+    <row r="200" spans="1:9">
+      <c r="A200" t="s">
+        <v>0</v>
+      </c>
+      <c r="B200" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C200">
+        <v>69.576106809999999</v>
+      </c>
+      <c r="D200">
+        <v>-138.90396720000001</v>
+      </c>
+      <c r="E200">
+        <v>2024</v>
+      </c>
+      <c r="F200" s="2">
+        <v>32.122779999999999</v>
+      </c>
+      <c r="G200" s="2">
+        <v>6.2787110000000004</v>
+      </c>
+      <c r="H200" s="3">
+        <v>223</v>
+      </c>
+      <c r="I200">
+        <v>58.533333333333339</v>
+      </c>
+    </row>
+    <row r="201" spans="1:9">
+      <c r="A201" t="s">
+        <v>0</v>
+      </c>
+      <c r="B201" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C201">
+        <v>69.576106809999999</v>
+      </c>
+      <c r="D201">
+        <v>-138.90396720000001</v>
+      </c>
+      <c r="E201">
+        <v>2024</v>
+      </c>
+      <c r="F201" s="2">
+        <v>32.122779999999999</v>
+      </c>
+      <c r="G201" s="2">
+        <v>6.2787110000000004</v>
+      </c>
+      <c r="H201" s="3">
+        <v>223</v>
+      </c>
+      <c r="I201">
+        <v>48.533333333333331</v>
+      </c>
+    </row>
+    <row r="202" spans="1:9">
+      <c r="A202" t="s">
+        <v>0</v>
+      </c>
+      <c r="B202" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C202">
+        <v>69.576106809999999</v>
+      </c>
+      <c r="D202">
+        <v>-138.90396720000001</v>
+      </c>
+      <c r="E202">
+        <v>2024</v>
+      </c>
+      <c r="F202" s="2">
+        <v>32.122779999999999</v>
+      </c>
+      <c r="G202" s="2">
+        <v>6.2787110000000004</v>
+      </c>
+      <c r="H202" s="3">
+        <v>223</v>
+      </c>
+      <c r="I202">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="203" spans="1:9">
+      <c r="A203" t="s">
+        <v>0</v>
+      </c>
+      <c r="B203" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C203">
+        <v>69.576106809999999</v>
+      </c>
+      <c r="D203">
+        <v>-138.90396720000001</v>
+      </c>
+      <c r="E203">
+        <v>2024</v>
+      </c>
+      <c r="F203" s="2">
+        <v>32.122779999999999</v>
+      </c>
+      <c r="G203" s="2">
+        <v>6.2787110000000004</v>
+      </c>
+      <c r="H203" s="3">
+        <v>223</v>
+      </c>
+      <c r="I203">
+        <v>49.800000000000004</v>
+      </c>
+    </row>
+    <row r="204" spans="1:9">
+      <c r="A204" t="s">
+        <v>0</v>
+      </c>
+      <c r="B204" t="s">
+        <v>6</v>
+      </c>
+      <c r="C204">
+        <v>69.575540020000005</v>
+      </c>
+      <c r="D204">
+        <v>-138.90445</v>
+      </c>
+      <c r="E204">
+        <v>2024</v>
+      </c>
+      <c r="F204" s="2">
+        <v>28.906300000000002</v>
+      </c>
+      <c r="G204" s="2">
+        <v>4.0111990000000004</v>
+      </c>
+      <c r="H204" s="3">
+        <v>223</v>
+      </c>
+      <c r="I204">
+        <v>35.166666666666664</v>
+      </c>
+    </row>
+    <row r="205" spans="1:9">
+      <c r="A205" t="s">
+        <v>0</v>
+      </c>
+      <c r="B205" t="s">
+        <v>6</v>
+      </c>
+      <c r="C205">
+        <v>69.575540020000005</v>
+      </c>
+      <c r="D205">
+        <v>-138.90445</v>
+      </c>
+      <c r="E205">
+        <v>2024</v>
+      </c>
+      <c r="F205" s="2">
+        <v>28.906300000000002</v>
+      </c>
+      <c r="G205" s="2">
+        <v>4.0111990000000004</v>
+      </c>
+      <c r="H205" s="3">
+        <v>223</v>
+      </c>
+      <c r="I205">
+        <v>53.6</v>
+      </c>
+    </row>
+    <row r="206" spans="1:9">
+      <c r="A206" t="s">
+        <v>0</v>
+      </c>
+      <c r="B206" t="s">
+        <v>6</v>
+      </c>
+      <c r="C206">
+        <v>69.575540020000005</v>
+      </c>
+      <c r="D206">
+        <v>-138.90445</v>
+      </c>
+      <c r="E206">
+        <v>2024</v>
+      </c>
+      <c r="F206" s="2">
+        <v>28.906300000000002</v>
+      </c>
+      <c r="G206" s="2">
+        <v>4.0111990000000004</v>
+      </c>
+      <c r="H206" s="3">
+        <v>223</v>
+      </c>
+      <c r="I206">
+        <v>53.233333333333327</v>
+      </c>
+    </row>
+    <row r="207" spans="1:9">
+      <c r="A207" t="s">
+        <v>0</v>
+      </c>
+      <c r="B207" t="s">
+        <v>6</v>
+      </c>
+      <c r="C207">
+        <v>69.575540020000005</v>
+      </c>
+      <c r="D207">
+        <v>-138.90445</v>
+      </c>
+      <c r="E207">
+        <v>2024</v>
+      </c>
+      <c r="F207" s="2">
+        <v>28.906300000000002</v>
+      </c>
+      <c r="G207" s="2">
+        <v>4.0111990000000004</v>
+      </c>
+      <c r="H207" s="3">
+        <v>223</v>
+      </c>
+      <c r="I207">
+        <v>51.5</v>
+      </c>
+    </row>
+    <row r="208" spans="1:9">
+      <c r="A208" t="s">
+        <v>0</v>
+      </c>
+      <c r="B208" t="s">
+        <v>6</v>
+      </c>
+      <c r="C208">
+        <v>69.575540020000005</v>
+      </c>
+      <c r="D208">
+        <v>-138.90445</v>
+      </c>
+      <c r="E208">
+        <v>2024</v>
+      </c>
+      <c r="F208" s="2">
+        <v>28.906300000000002</v>
+      </c>
+      <c r="G208" s="2">
+        <v>4.0111990000000004</v>
+      </c>
+      <c r="H208" s="3">
+        <v>223</v>
+      </c>
+      <c r="I208">
+        <v>56.4</v>
+      </c>
+    </row>
+    <row r="209" spans="1:9">
+      <c r="A209" t="s">
+        <v>0</v>
+      </c>
+      <c r="B209" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C209">
+        <v>69.575888039999995</v>
+      </c>
+      <c r="D209">
+        <v>-138.90355299999999</v>
+      </c>
+      <c r="E209">
+        <v>2024</v>
+      </c>
+      <c r="F209" s="2">
+        <v>29.5139</v>
+      </c>
+      <c r="G209" s="2">
+        <v>7.6486470000000004</v>
+      </c>
+      <c r="H209" s="3">
+        <v>223</v>
+      </c>
+      <c r="I209">
+        <v>67.233333333333334</v>
+      </c>
+    </row>
+    <row r="210" spans="1:9">
+      <c r="A210" t="s">
+        <v>0</v>
+      </c>
+      <c r="B210" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C210">
+        <v>69.575888039999995</v>
+      </c>
+      <c r="D210">
+        <v>-138.90355299999999</v>
+      </c>
+      <c r="E210">
+        <v>2024</v>
+      </c>
+      <c r="F210" s="2">
+        <v>29.5139</v>
+      </c>
+      <c r="G210" s="2">
+        <v>7.6486470000000004</v>
+      </c>
+      <c r="H210" s="3">
+        <v>223</v>
+      </c>
+      <c r="I210">
+        <v>54.066666666666663</v>
+      </c>
+    </row>
+    <row r="211" spans="1:9">
+      <c r="A211" t="s">
+        <v>0</v>
+      </c>
+      <c r="B211" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C211">
+        <v>69.575888039999995</v>
+      </c>
+      <c r="D211">
+        <v>-138.90355299999999</v>
+      </c>
+      <c r="E211">
+        <v>2024</v>
+      </c>
+      <c r="F211" s="2">
+        <v>29.5139</v>
+      </c>
+      <c r="G211" s="2">
+        <v>7.6486470000000004</v>
+      </c>
+      <c r="H211" s="3">
+        <v>223</v>
+      </c>
+      <c r="I211">
+        <v>65.266666666666666</v>
+      </c>
+    </row>
+    <row r="212" spans="1:9">
+      <c r="A212" t="s">
+        <v>0</v>
+      </c>
+      <c r="B212" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C212">
+        <v>69.575888039999995</v>
+      </c>
+      <c r="D212">
+        <v>-138.90355299999999</v>
+      </c>
+      <c r="E212">
+        <v>2024</v>
+      </c>
+      <c r="F212" s="2">
+        <v>29.5139</v>
+      </c>
+      <c r="G212" s="2">
+        <v>7.6486470000000004</v>
+      </c>
+      <c r="H212" s="3">
+        <v>223</v>
+      </c>
+      <c r="I212">
+        <v>63.233333333333327</v>
+      </c>
+    </row>
+    <row r="213" spans="1:9">
+      <c r="A213" t="s">
+        <v>0</v>
+      </c>
+      <c r="B213" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C213">
+        <v>69.575888039999995</v>
+      </c>
+      <c r="D213">
+        <v>-138.90355299999999</v>
+      </c>
+      <c r="E213">
+        <v>2024</v>
+      </c>
+      <c r="F213" s="2">
+        <v>29.5139</v>
+      </c>
+      <c r="G213" s="2">
+        <v>7.6486470000000004</v>
+      </c>
+      <c r="H213" s="3">
+        <v>223</v>
+      </c>
+      <c r="I213">
+        <v>66.5</v>
+      </c>
+    </row>
+    <row r="214" spans="1:9">
+      <c r="A214" t="s">
+        <v>0</v>
+      </c>
+      <c r="B214" t="s">
+        <v>3</v>
+      </c>
+      <c r="C214">
+        <v>69.574881039999994</v>
+      </c>
+      <c r="D214">
+        <v>-138.86307059999999</v>
+      </c>
+      <c r="E214">
+        <v>2024</v>
+      </c>
+      <c r="F214" s="2">
+        <v>71.664990000000003</v>
+      </c>
+      <c r="G214" s="2">
+        <v>1.0686739999999999</v>
+      </c>
+      <c r="H214" s="3">
+        <v>224</v>
+      </c>
+      <c r="I214">
+        <v>48.433333333333337</v>
+      </c>
+    </row>
+    <row r="215" spans="1:9">
+      <c r="A215" t="s">
+        <v>0</v>
+      </c>
+      <c r="B215" t="s">
+        <v>3</v>
+      </c>
+      <c r="C215">
+        <v>69.574888920000006</v>
+      </c>
+      <c r="D215">
+        <v>-138.8631728</v>
+      </c>
+      <c r="E215">
+        <v>2024</v>
+      </c>
+      <c r="F215" s="2">
+        <v>71.566590000000005</v>
+      </c>
+      <c r="G215" s="2">
+        <v>3.236253</v>
+      </c>
+      <c r="H215" s="3">
+        <v>224</v>
+      </c>
+      <c r="I215">
+        <v>48.4</v>
+      </c>
+    </row>
+    <row r="216" spans="1:9">
+      <c r="A216" t="s">
+        <v>0</v>
+      </c>
+      <c r="B216" t="s">
+        <v>3</v>
+      </c>
+      <c r="C216">
+        <v>69.574882380000005</v>
+      </c>
+      <c r="D216">
+        <v>-138.8634658</v>
+      </c>
+      <c r="E216">
+        <v>2024</v>
+      </c>
+      <c r="F216" s="2">
+        <v>71.334130000000002</v>
+      </c>
+      <c r="G216" s="2">
+        <v>2.6920440000000001</v>
+      </c>
+      <c r="H216" s="3">
+        <v>224</v>
+      </c>
+      <c r="I216">
+        <v>38.6</v>
+      </c>
+    </row>
+    <row r="217" spans="1:9">
+      <c r="A217" t="s">
+        <v>0</v>
+      </c>
+      <c r="B217" t="s">
+        <v>3</v>
+      </c>
+      <c r="C217">
+        <v>69.574860330000007</v>
+      </c>
+      <c r="D217">
+        <v>-138.8637913</v>
+      </c>
+      <c r="E217">
+        <v>2024</v>
+      </c>
+      <c r="F217" s="2">
+        <v>71.194389999999999</v>
+      </c>
+      <c r="G217" s="2">
+        <v>1.1705080000000001</v>
+      </c>
+      <c r="H217" s="3">
+        <v>224</v>
+      </c>
+      <c r="I217">
+        <v>40.133333333333333</v>
+      </c>
+    </row>
+    <row r="218" spans="1:9">
+      <c r="A218" t="s">
+        <v>0</v>
+      </c>
+      <c r="B218" t="s">
+        <v>3</v>
+      </c>
+      <c r="C218">
+        <v>69.574861170000005</v>
+      </c>
+      <c r="D218">
+        <v>-138.86387010000001</v>
+      </c>
+      <c r="E218">
+        <v>2024</v>
+      </c>
+      <c r="F218" s="2">
+        <v>71.170460000000006</v>
+      </c>
+      <c r="G218" s="2">
+        <v>1.1862360000000001</v>
+      </c>
+      <c r="H218" s="3">
+        <v>224</v>
+      </c>
+      <c r="I218">
+        <v>39.06666666666667</v>
+      </c>
+    </row>
+    <row r="219" spans="1:9">
+      <c r="A219" t="s">
+        <v>0</v>
+      </c>
+      <c r="B219" t="s">
+        <v>3</v>
+      </c>
+      <c r="C219">
+        <v>69.574857399999999</v>
+      </c>
+      <c r="D219">
+        <v>-138.8640747</v>
+      </c>
+      <c r="E219">
+        <v>2024</v>
+      </c>
+      <c r="F219" s="2">
+        <v>71.030659999999997</v>
+      </c>
+      <c r="G219" s="2">
+        <v>1.785264</v>
+      </c>
+      <c r="H219" s="3">
+        <v>224</v>
+      </c>
+      <c r="I219">
+        <v>46.199999999999996</v>
+      </c>
+    </row>
+    <row r="220" spans="1:9">
+      <c r="A220" t="s">
+        <v>0</v>
+      </c>
+      <c r="B220" t="s">
+        <v>4</v>
+      </c>
+      <c r="C220">
+        <v>69.576416179999995</v>
+      </c>
+      <c r="D220">
+        <v>-138.86817970000001</v>
+      </c>
+      <c r="E220">
+        <v>2024</v>
+      </c>
+      <c r="F220" s="2">
+        <v>71.11157</v>
+      </c>
+      <c r="G220" s="2">
+        <v>3.3767399999999999</v>
+      </c>
+      <c r="H220" s="3">
+        <v>224</v>
+      </c>
+      <c r="I220">
+        <v>66.36666666666666</v>
+      </c>
+    </row>
+    <row r="221" spans="1:9">
+      <c r="A221" t="s">
+        <v>0</v>
+      </c>
+      <c r="B221" t="s">
+        <v>4</v>
+      </c>
+      <c r="C221">
+        <v>69.576403529999993</v>
+      </c>
+      <c r="D221">
+        <v>-138.86811879999999</v>
+      </c>
+      <c r="E221">
+        <v>2024</v>
+      </c>
+      <c r="F221" s="2">
+        <v>71.146529999999998</v>
+      </c>
+      <c r="G221" s="2">
+        <v>2.5742989999999999</v>
+      </c>
+      <c r="H221" s="3">
+        <v>224</v>
+      </c>
+      <c r="I221">
+        <v>64.8</v>
+      </c>
+    </row>
+    <row r="222" spans="1:9">
+      <c r="A222" t="s">
+        <v>0</v>
+      </c>
+      <c r="B222" t="s">
+        <v>4</v>
+      </c>
+      <c r="C222">
+        <v>69.576461190000003</v>
+      </c>
+      <c r="D222">
+        <v>-138.86773909999999</v>
+      </c>
+      <c r="E222">
+        <v>2024</v>
+      </c>
+      <c r="F222" s="2">
+        <v>71.806269999999998</v>
+      </c>
+      <c r="G222" s="2">
+        <v>4.376296</v>
+      </c>
+      <c r="H222" s="3">
+        <v>224</v>
+      </c>
+      <c r="I222">
+        <v>65.566666666666663</v>
+      </c>
+    </row>
+    <row r="223" spans="1:9">
+      <c r="A223" t="s">
+        <v>0</v>
+      </c>
+      <c r="B223" t="s">
+        <v>4</v>
+      </c>
+      <c r="C223">
+        <v>69.576468489999996</v>
+      </c>
+      <c r="D223">
+        <v>-138.8676384</v>
+      </c>
+      <c r="E223">
+        <v>2024</v>
+      </c>
+      <c r="F223" s="2">
+        <v>71.979259999999996</v>
+      </c>
+      <c r="G223" s="2">
+        <v>4.6941449999999998</v>
+      </c>
+      <c r="H223" s="3">
+        <v>224</v>
+      </c>
+      <c r="I223">
+        <v>76.933333333333337</v>
+      </c>
+    </row>
+    <row r="224" spans="1:9">
+      <c r="A224" t="s">
+        <v>0</v>
+      </c>
+      <c r="B224" t="s">
+        <v>4</v>
+      </c>
+      <c r="C224">
+        <v>69.576505789999999</v>
+      </c>
+      <c r="D224">
+        <v>-138.86729539999999</v>
+      </c>
+      <c r="E224">
+        <v>2024</v>
+      </c>
+      <c r="F224" s="2">
+        <v>72.876679999999993</v>
+      </c>
+      <c r="G224" s="2">
+        <v>2.3661750000000001</v>
+      </c>
+      <c r="H224" s="3">
+        <v>224</v>
+      </c>
+      <c r="I224">
+        <v>69.36666666666666</v>
+      </c>
+    </row>
+    <row r="225" spans="1:9">
+      <c r="A225" t="s">
+        <v>0</v>
+      </c>
+      <c r="B225" t="s">
+        <v>4</v>
+      </c>
+      <c r="C225">
+        <v>69.576544850000005</v>
+      </c>
+      <c r="D225">
+        <v>-138.86699780000001</v>
+      </c>
+      <c r="E225">
+        <v>2024</v>
+      </c>
+      <c r="F225" s="2">
+        <v>73.514600000000002</v>
+      </c>
+      <c r="G225" s="2">
+        <v>4.204345</v>
+      </c>
+      <c r="H225" s="3">
+        <v>224</v>
+      </c>
+      <c r="I225">
+        <v>69.899999999999991</v>
       </c>
     </row>
   </sheetData>
